--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28502"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="473" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73C6FCED-64A6-499B-8994-0D2F56FC0749}"/>
+  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A90A03-9369-43FD-8338-648F40D68E59}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -44,23 +44,17 @@
     <t xml:space="preserve">OCORRENCIA_INTERNA                                     </t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -86,13 +80,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -142,14 +129,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,25 +465,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15">
-      <c r="A2" s="4">
-        <v>665370999</v>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>731205773</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
-      <c r="A3" s="4">
-        <v>637848114</v>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>707886374</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15">
-      <c r="A4" s="4">
-        <v>538421813</v>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>706283367</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -505,291 +491,590 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>733588481</v>
+        <v>717743797</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>702566534</v>
+        <v>711165229</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>715207027</v>
+        <v>705864621</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>733905057</v>
+        <v>704636566</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>716103027</v>
+        <v>691260222</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>691023000</v>
+        <v>685579215</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>676793213</v>
+        <v>681791285</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>671309148</v>
+        <v>677449120</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>662906290</v>
+        <v>668149549</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>654912868</v>
+        <v>639555055</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>651302188</v>
+        <v>631520891</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>645812920</v>
+        <v>664011248</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>644588232</v>
+        <v>652269089</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>642053742</v>
+        <v>734285681</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>600699429</v>
+        <v>619868825</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>599169228</v>
+        <v>613503097</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>595308655</v>
+        <v>605900368</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>595920285</v>
+        <v>598334609</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>708875889</v>
+        <v>594674115</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>643625563</v>
+        <v>594402764</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>648942997</v>
+        <v>589295272</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>670129521</v>
+        <v>578597837</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>664362153</v>
+        <v>578428975</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>721303935</v>
+        <v>573545245</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>706339771</v>
+        <v>558810671</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>733019099</v>
+        <v>545321857</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>733019131</v>
+        <v>174658579</v>
       </c>
       <c r="B31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>733019123</v>
+        <v>173440250</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>733019115</v>
+        <v>724821784</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>733019107</v>
+        <v>723868455</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>733019081</v>
+        <v>723018606</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>721557597</v>
+        <v>722508755</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="3"/>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="3"/>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="3"/>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="3"/>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="3"/>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="3"/>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="3"/>
-    </row>
-    <row r="77" spans="1:1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>720952005</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>734325263</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>734777539</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>570710354</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>597618150</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>538407259</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>527424836</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>663093072</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>684666062</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>641297290</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>645136833</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>729528350</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>604719975</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>651478848</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>689983751</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>655512469</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>656568023</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>647184138</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>671416778</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>663783862</v>
+      </c>
+      <c r="B56" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>600172096</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>620190474</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>735103073</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>734714938</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>718842499</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>663091597</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>678333711</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>580730699</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>720571599</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>549877508</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>541298059</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>718544954</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>710179171</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>718021268</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>661444657</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>660101241</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>735192902</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>734342052</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>522313836</v>
+      </c>
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>604552285</v>
+      </c>
+      <c r="B76" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:2">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:2">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:2">
       <c r="A80" s="3"/>
     </row>
     <row r="81" spans="1:1">

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA7B1FC-8F05-4653-BE2D-0E9E5405BB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="530" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB92EC58-823D-408E-A905-18771CB5CC3E}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="-120" windowWidth="19530" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
+    <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -49,15 +49,12 @@
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -75,12 +72,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -132,14 +123,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -160,7 +150,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -456,14 +446,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B66"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="51.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -471,221 +461,340 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>756341560</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>749627778</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>748785783</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>747322885</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>739538282</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>727679775</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>704323504</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>690884303</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>684964384</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>680929068</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>664150160</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>660469713</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>650063088</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>594429841</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>553660485</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>740162130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>555865991</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>749296533</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>738016371</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>737897953</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>737670921</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>708620574</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>703626543</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>690022367</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>688378110</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>660460894</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>631584731</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>615996190</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>614842965</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>592398964</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>558603415</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>564922791</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>735026779</v>
-      </c>
-      <c r="B17" s="4" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>748224338</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>742567369</v>
-      </c>
-      <c r="B18" s="4" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>658389931</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>753515117</v>
-      </c>
-      <c r="B19" s="4" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>713227340</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>753513815</v>
-      </c>
-      <c r="B20" s="4" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>638633481</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>751624176</v>
-      </c>
-      <c r="B21" s="4" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>552140513</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>749066472</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>751624168</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>635611233</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>551963949</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>671764037</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>749747733</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>664198672</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>2</v>
-      </c>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>738507510</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>749502070</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>650671039</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>747357485</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>175266091</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>175265960</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="3"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="3"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="3"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="3"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="3"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="3"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="3"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="3"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="3"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="3"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="3"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="3"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="3"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="3"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28528"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="530" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB92EC58-823D-408E-A905-18771CB5CC3E}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F8009F-1FA4-454B-87BA-C19B4D5695B5}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -463,15 +463,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>740162130</v>
-      </c>
-      <c r="B2" t="s">
+        <v>572736118</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>555865991</v>
+        <v>667057602</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
@@ -479,15 +479,15 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>749296533</v>
+        <v>750304622</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>738016371</v>
+        <v>750174561</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>737897953</v>
+        <v>737876627</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>737670921</v>
+        <v>737689061</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
@@ -511,7 +511,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>708620574</v>
+        <v>680125360</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>703626543</v>
+        <v>667301646</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>2</v>
@@ -527,7 +527,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>690022367</v>
+        <v>658231562</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>2</v>
@@ -535,7 +535,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>688378110</v>
+        <v>644261251</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>2</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>660460894</v>
+        <v>590268607</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
@@ -551,7 +551,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>631584731</v>
+        <v>558947556</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>2</v>
@@ -559,39 +559,39 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>615996190</v>
+        <v>613251382</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>614842965</v>
+        <v>690276526</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>592398964</v>
+        <v>724610377</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>558603415</v>
+        <v>744373246</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>564922791</v>
+        <v>739685646</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>3</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>748224338</v>
+        <v>669224333</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>3</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>658389931</v>
+        <v>638301683</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>3</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>713227340</v>
+        <v>657805390</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>3</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>638633481</v>
+        <v>658424795</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>3</v>
@@ -631,15 +631,15 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>552140513</v>
+        <v>746664840</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>738507510</v>
+        <v>674742030</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>2</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>749502070</v>
+        <v>665074393</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>2</v>
@@ -655,35 +655,20 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>650671039</v>
+        <v>750480422</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27">
-        <v>747357485</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28">
-        <v>175266091</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29">
-        <v>175265960</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B29" s="3"/>
     </row>
     <row r="30" spans="1:2">
       <c r="B30" s="3"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F8009F-1FA4-454B-87BA-C19B4D5695B5}"/>
+  <xr:revisionPtr revIDLastSave="543" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D50BA18-1EA4-4976-996F-2DDBF1992DF6}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="6">
   <si>
     <t>Recibo</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -450,7 +456,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
@@ -463,7 +469,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>572736118</v>
+        <v>756964585</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -471,7 +477,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>667057602</v>
+        <v>739500704</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
@@ -479,15 +485,15 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>750304622</v>
+        <v>739387250</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>750174561</v>
+        <v>541113019</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -495,7 +501,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>737876627</v>
+        <v>173725106</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
@@ -503,103 +509,103 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>737689061</v>
+        <v>741675726</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>680125360</v>
+        <v>732735273</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>667301646</v>
+        <v>675782126</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>658231562</v>
+        <v>592394039</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>644261251</v>
+        <v>632469940</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>590268607</v>
+        <v>691294338</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>558947556</v>
+        <v>740683150</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>613251382</v>
+        <v>740361773</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>690276526</v>
+        <v>704389562</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>724610377</v>
+        <v>730203035</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>744373246</v>
+        <v>628838520</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>739685646</v>
+        <v>750957601</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>669224333</v>
+        <v>607371949</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>3</v>
@@ -607,59 +613,34 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>638301683</v>
+        <v>750972535</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>657805390</v>
+        <v>751031786</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22">
-        <v>658424795</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B22" s="3"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23">
-        <v>746664840</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24">
-        <v>674742030</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B24" s="3"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25">
-        <v>665074393</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B25" s="3"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26">
-        <v>750480422</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B26" s="3"/>
     </row>
     <row r="27" spans="1:2">
       <c r="B27" s="3"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28602"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="543" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D50BA18-1EA4-4976-996F-2DDBF1992DF6}"/>
+  <xr:revisionPtr revIDLastSave="549" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D0DBA39-0240-4576-AAB8-FA61313AD0DD}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="6">
   <si>
     <t>Recibo</t>
   </si>
@@ -44,23 +44,23 @@
     <t xml:space="preserve">OCORRENCIA_INTERNA                                     </t>
   </si>
   <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+    <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -78,6 +78,18 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -129,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -138,6 +150,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B239"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -469,298 +483,1907 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>756964585</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>517620104</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>739500704</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>491387258</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>739387250</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>507714206</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>541113019</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>505866297</v>
+      </c>
+      <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>173725106</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>549643199</v>
+      </c>
+      <c r="B6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>741675726</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>3</v>
+        <v>567811868</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>732735273</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>3</v>
+        <v>533091900</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>675782126</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>3</v>
+        <v>565194267</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>592394039</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>495766457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="4">
+        <v>458031238</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="4">
+        <v>455265060</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="4">
+        <v>573229626</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="4">
+        <v>540194499</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="4">
+        <v>557287004</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="4">
+        <v>559636273</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4">
+        <v>459136291</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4">
+        <v>507714214</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="4">
+        <v>564131823</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="4">
+        <v>470776539</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="4">
+        <v>505866305</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="4">
+        <v>449192958</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="4">
+        <v>513304950</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="4">
+        <v>567811876</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4">
+        <v>565194275</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15">
+      <c r="A26" s="5">
+        <v>495766465</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15">
+      <c r="A27" s="5">
+        <v>478617289</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="4">
+        <v>557300849</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="4">
+        <v>501945194</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="4">
+        <v>566306340</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="4">
+        <v>557287012</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="4">
+        <v>445746005</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>505866313</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>567811884</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>495766473</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>576052041</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>556006793</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>567089697</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>557287020</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>505866321</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>612260806</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>583709211</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>567811892</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>495766481</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>517085324</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>517675868</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>556006801</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>557287038</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>560177150</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>603488424</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="4">
+        <v>631539602</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="4">
+        <v>505866339</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="4">
+        <v>633431865</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="4">
+        <v>517675876</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="4">
+        <v>567096221</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="4">
+        <v>537756953</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="4">
+        <v>603488432</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="4">
+        <v>525999680</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="4">
+        <v>551503604</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="4">
+        <v>513073126</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="4">
+        <v>567096239</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="4">
+        <v>641744713</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="4">
+        <v>685873618</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="4">
+        <v>589925001</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="4">
+        <v>537506432</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="4">
+        <v>597241904</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="4">
+        <v>597663800</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="4">
+        <v>601490851</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="4">
+        <v>559469832</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="4">
+        <v>627461043</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="4">
+        <v>603488440</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="4">
+        <v>604669642</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="4">
+        <v>579029657</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="4">
+        <v>562090229</v>
+      </c>
+      <c r="B74" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>632469940</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="75" spans="1:2">
+      <c r="A75" s="4">
+        <v>526883727</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="4">
+        <v>583763846</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="4">
+        <v>521810485</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="4">
+        <v>565421926</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="4">
+        <v>683190577</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="4">
+        <v>583172139</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="4">
+        <v>611689245</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="4">
+        <v>587868195</v>
+      </c>
+      <c r="B82" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="4">
+        <v>706552258</v>
+      </c>
+      <c r="B83" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="4">
+        <v>551503612</v>
+      </c>
+      <c r="B84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="4">
+        <v>651374369</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>606289753</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>633770247</v>
+      </c>
+      <c r="B87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>555054505</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>665806620</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>694335666</v>
+      </c>
+      <c r="B90" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>713542318</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>665951434</v>
+      </c>
+      <c r="B92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>641744721</v>
+      </c>
+      <c r="B93" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>567096247</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>589925019</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>684464948</v>
+      </c>
+      <c r="B96" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>634144301</v>
+      </c>
+      <c r="B97" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>533059519</v>
+      </c>
+      <c r="B98" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>669268611</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>578048468</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>671278004</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>558348318</v>
+      </c>
+      <c r="B102" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>559469840</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>601490869</v>
+      </c>
+      <c r="B104" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>601722469</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>620879944</v>
+      </c>
+      <c r="B106" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>648632788</v>
+      </c>
+      <c r="B107" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>694779426</v>
+      </c>
+      <c r="B108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>673135111</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>627461050</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>542501360</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>564239022</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>582422782</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>699365940</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>628782017</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>667549160</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>583763853</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>654833973</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>565421934</v>
+      </c>
+      <c r="B119" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>607255316</v>
+      </c>
+      <c r="B120" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>567140565</v>
+      </c>
+      <c r="B121" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>679576904</v>
+      </c>
+      <c r="B122" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>703840474</v>
+      </c>
+      <c r="B123" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>583172147</v>
+      </c>
+      <c r="B124" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>606096646</v>
+      </c>
+      <c r="B125" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>629666102</v>
+      </c>
+      <c r="B126" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>681464206</v>
+      </c>
+      <c r="B127" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>704784713</v>
+      </c>
+      <c r="B128" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>549905523</v>
+      </c>
+      <c r="B129" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>705322265</v>
+      </c>
+      <c r="B130" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>726470242</v>
+      </c>
+      <c r="B131" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>704521743</v>
+      </c>
+      <c r="B132" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>654600653</v>
+      </c>
+      <c r="B133" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>679259113</v>
+      </c>
+      <c r="B134" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>679560304</v>
+      </c>
+      <c r="B135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>551503620</v>
+      </c>
+      <c r="B136" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>699777599</v>
+      </c>
+      <c r="B137" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>660331731</v>
+      </c>
+      <c r="B138" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>684950425</v>
+      </c>
+      <c r="B139" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>706036468</v>
+      </c>
+      <c r="B140" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>593844016</v>
+      </c>
+      <c r="B141" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>573094517</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>594779401</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>655400079</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>595889845</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>735882346</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>574893081</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>567096254</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>713503872</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>560789269</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>666471432</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>603123922</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>589925027</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>644077095</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>737228324</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>620586069</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>664631631</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>667051381</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>680348277</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>669451977</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>645909890</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>670606692</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>598417594</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>746184609</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>170978435</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>743790994</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>670576044</v>
+      </c>
+      <c r="B167" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>691294338</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>740683150</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>740361773</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>704389562</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>730203035</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>628838520</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>750957601</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>607371949</v>
-      </c>
-      <c r="B19" s="3" t="s">
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>545071957</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>174607840</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>650280898</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>645029939</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>635363900</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>632050484</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>618911097</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>572726465</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>567210608</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>554483259</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>174606735</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>173046289</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>174456370</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>174456354</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>664752296</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>743128831</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>751195169</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>751195151</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>733595783</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>731116301</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>731053066</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>728316906</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>721464083</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>720890213</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>712215528</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>704714447</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>699148452</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>688408685</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>688342074</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>685327904</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>682006758</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>674237148</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>671364614</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>664055146</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>688710791</v>
+      </c>
+      <c r="B202" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>750972535</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>751031786</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="B26" s="3"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="B31" s="3"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="B32" s="3"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="3"/>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="3"/>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="3"/>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="3"/>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="3"/>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="3"/>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" s="3"/>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="3"/>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="3"/>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="3"/>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="3"/>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="3"/>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="3"/>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="3"/>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="3"/>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="3"/>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="3"/>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="3"/>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="3"/>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="3"/>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" s="3"/>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" s="3"/>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>644085429</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>716384338</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>752395636</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>757562909</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>757562891</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>723949982</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>704323108</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>699768036</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>704125586</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>623425083</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>661393961</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>660568845</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>633750074</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>611088075</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>743038592</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>751808787</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>600408524</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>613079049</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>564669715</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>661478168</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>625958875</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>633717032</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>640511931</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>721576290</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>615816760</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>569056058</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>627038379</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>616519447</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>657091124</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>655624694</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>560482964</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>703106066</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>724190636</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>752798532</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>753544414</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>752823298</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>728195532</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28605"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="553" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17D4CC9C-FF86-4DF4-91D1-5EF552F2EB5C}"/>
+  <xr:revisionPtr revIDLastSave="557" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{634C75CD-8560-4BFC-AEC4-D7DA0E8C6904}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="6">
   <si>
     <t>Recibo</t>
   </si>
@@ -44,10 +44,16 @@
     <t xml:space="preserve">OCORRENCIA_INTERNA                                     </t>
   </si>
   <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -143,7 +149,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -476,7 +487,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>755023847</v>
+        <v>710744388</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -484,7 +495,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>746806946</v>
+        <v>711452668</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -492,151 +503,151 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>743837720</v>
+        <v>762420457</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>759766219</v>
+        <v>761557820</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>761475098</v>
+        <v>734894987</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>743309423</v>
+        <v>676548971</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>727391322</v>
+        <v>664191800</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>722818824</v>
+        <v>659296937</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>721064511</v>
+        <v>657123273</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>718078151</v>
+        <v>654553365</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>713314858</v>
+        <v>630058521</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>706468026</v>
+        <v>617516988</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>703399000</v>
+        <v>621889942</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>691685394</v>
+        <v>722974916</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>656983677</v>
+        <v>750967618</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>647005069</v>
+        <v>670053879</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>644855144</v>
+        <v>673457275</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>541267211</v>
+        <v>755362260</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>174795454</v>
+        <v>742608510</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>171064813</v>
+        <v>739658494</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>754298705</v>
+        <v>755426628</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>3</v>
@@ -644,15 +655,15 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>728182373</v>
+        <v>722937939</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>753605504</v>
+        <v>684221256</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>3</v>
@@ -660,7 +671,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>676112422</v>
+        <v>755662594</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>3</v>
@@ -668,7 +679,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>693780896</v>
+        <v>754734436</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>3</v>
@@ -676,419 +687,164 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>666709278</v>
+        <v>649336314</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28">
-        <v>568586212</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29">
-        <v>565535832</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B29" s="3"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30">
-        <v>601157351</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B30" s="3"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31">
-        <v>754718603</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B31" s="3"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32">
-        <v>555706237</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>743358826</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>743328506</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>732434224</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>721095457</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>705245615</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>695159693</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>690542190</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>687960801</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>687847958</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>684352689</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>682507581</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>682113299</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>681537274</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>677719530</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>661274260</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>557518424</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>174694079</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>740608298</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>680131343</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>680310707</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>669235859</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>652306907</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>630758666</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>749244004</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>749244608</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>732770221</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>737326383</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
-        <v>747457400</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
-        <v>701325924</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
-        <v>712766637</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63">
-        <v>709349223</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64">
-        <v>671091662</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="3"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="3"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="3"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="3"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="3"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="3"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="3"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="3"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="3"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="3"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="3"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="3"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="3"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="3"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="3"/>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65">
-        <v>639738941</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B65" s="3"/>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66">
-        <v>573697491</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B66" s="3"/>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67">
-        <v>651433991</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B67" s="3"/>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68">
-        <v>723381871</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B68" s="3"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69">
-        <v>577105897</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B69" s="3"/>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70">
-        <v>738094485</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B70" s="3"/>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71">
-        <v>734185576</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B71" s="3"/>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72">
-        <v>691210672</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B72" s="3"/>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73">
-        <v>657262576</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B73" s="3"/>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74">
-        <v>656932732</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B74" s="3"/>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75">
-        <v>588297824</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B75" s="3"/>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76">
-        <v>549246043</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B76" s="3"/>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77">
-        <v>625969575</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B77" s="3"/>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78">
-        <v>745337331</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B78" s="3"/>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="4"/>
@@ -1406,7 +1162,10 @@
       <c r="B239" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A78">
+  <conditionalFormatting sqref="A28:A78">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5634554F-56AB-41E5-B4B9-376A15A3AE65}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67E449CE-E922-4C6D-9807-2ED6731F83C5}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+    <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
 </sst>
 </file>
@@ -139,7 +139,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -482,7 +492,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>731827733</v>
+        <v>728823893</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -490,7 +500,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>736635339</v>
+        <v>727822631</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
@@ -498,7 +508,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>750120325</v>
+        <v>727681722</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -506,7 +516,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>750103180</v>
+        <v>726683869</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -514,7 +524,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>746688559</v>
+        <v>718985678</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
@@ -522,7 +532,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>743259826</v>
+        <v>703019913</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
@@ -530,7 +540,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>723018614</v>
+        <v>747826265</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
@@ -538,7 +548,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>721075202</v>
+        <v>702729678</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>2</v>
@@ -546,7 +556,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>720952013</v>
+        <v>689992539</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>2</v>
@@ -554,15 +564,15 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>719378915</v>
+        <v>626065365</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>715889725</v>
+        <v>581344839</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
@@ -570,7 +580,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>708091131</v>
+        <v>743619243</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>2</v>
@@ -578,7 +588,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>669954749</v>
+        <v>736879036</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
@@ -586,7 +596,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>663770091</v>
+        <v>724549435</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
@@ -594,7 +604,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>639399009</v>
+        <v>723311738</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>2</v>
@@ -602,7 +612,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>632514448</v>
+        <v>710037775</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>2</v>
@@ -610,63 +620,63 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>596657894</v>
+        <v>707194704</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>755563446</v>
+        <v>702380605</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>695959092</v>
+        <v>696305246</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>716268226</v>
+        <v>691559730</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>721990202</v>
+        <v>690493709</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>563097389</v>
+        <v>690487768</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>632836635</v>
+        <v>690060433</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>760316806</v>
+        <v>689454043</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>2</v>
@@ -674,7 +684,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>759554052</v>
+        <v>683060663</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>2</v>
@@ -682,7 +692,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>756945824</v>
+        <v>677430393</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>2</v>
@@ -690,7 +700,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>731696021</v>
+        <v>670525090</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>2</v>
@@ -698,7 +708,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>563464555</v>
+        <v>641812205</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>2</v>
@@ -706,7 +716,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>760815823</v>
+        <v>635293735</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>2</v>
@@ -714,7 +724,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>760779052</v>
+        <v>581344821</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>2</v>
@@ -722,7 +732,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>759194339</v>
+        <v>578157251</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
@@ -730,47 +740,47 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>751901210</v>
+        <v>575157270</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>750097010</v>
+        <v>723936377</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>714717646</v>
+        <v>738692528</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>699582007</v>
+        <v>700569688</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>692228202</v>
+        <v>619634367</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>676451523</v>
+        <v>577605078</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>2</v>
@@ -778,7 +788,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>671078313</v>
+        <v>677719167</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>2</v>
@@ -786,147 +796,82 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>646625511</v>
+        <v>678640826</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41">
-        <v>626881845</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B41" s="3"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42">
-        <v>761028434</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B42" s="3"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43">
-        <v>691834745</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B43" s="3"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44">
-        <v>682501550</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B44" s="3"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45">
-        <v>701812277</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="B45" s="3"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46">
-        <v>568026912</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="B46" s="3"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47">
-        <v>748564154</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B47" s="3"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48">
-        <v>760739015</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>169537598</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>661039747</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>732737519</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>760868293</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>750634275</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+      <c r="B48" s="3"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="3"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="3"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="2:2">
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="2:2">
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="2:2">
       <c r="B56" s="3"/>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="2:2">
       <c r="B57" s="3"/>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="2:2">
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="2:2">
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="2:2">
       <c r="B60" s="3"/>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="2:2">
       <c r="B61" s="3"/>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="2:2">
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="2:2">
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="2:2">
       <c r="B64" s="3"/>
     </row>
     <row r="65" spans="2:2">
@@ -1456,12 +1401,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A54:A90">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A91:A143">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:A53">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A91:A143">
+  <conditionalFormatting sqref="A2:A10">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A53">
+  <conditionalFormatting sqref="A11:A40">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="597" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6BD2601-20D1-4D2E-BFBC-5D88776A3929}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D464BAE-221B-46D1-B989-171C7DD9E502}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
   <si>
     <t xml:space="preserve">OCORRENCIA_INTERNA                                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
@@ -135,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -148,11 +145,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -495,39 +498,39 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>729612295</v>
+        <v>742207420</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3">
-        <v>635415692</v>
+      <c r="A3" s="6">
+        <v>642045151</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4">
-        <v>650488855</v>
+      <c r="A4" s="6">
+        <v>755441163</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5">
-        <v>717701746</v>
+      <c r="A5" s="6">
+        <v>730464975</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6">
-        <v>752468094</v>
+      <c r="A6" s="6">
+        <v>709879740</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
@@ -535,31 +538,31 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>763607292</v>
+        <v>635221421</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>175483118</v>
+        <v>652918065</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>646222210</v>
+        <v>721974206</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>650969995</v>
+        <v>766224954</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>3</v>
@@ -567,151 +570,151 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>682542646</v>
+        <v>171478237</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>679683007</v>
+        <v>755523044</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>624692632</v>
+        <v>724553726</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>628607933</v>
+        <v>744902796</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>590277111</v>
+        <v>717055432</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>169464124</v>
+        <v>716995406</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>718827797</v>
+        <v>713274276</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>173520796</v>
+        <v>694190038</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>173842257</v>
+        <v>659705705</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>761931710</v>
+        <v>680094053</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>666929322</v>
+        <v>678119615</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>552234894</v>
+        <v>671957771</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>173835863</v>
+        <v>669910824</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>762043705</v>
+        <v>640466789</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>724833094</v>
+        <v>651547469</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>714697335</v>
+        <v>645744727</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>763926528</v>
+        <v>610572319</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>740941921</v>
+        <v>173161492</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>746184849</v>
+        <v>670056369</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>3</v>
@@ -719,7 +722,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>741845154</v>
+        <v>670529597</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>3</v>
@@ -727,7 +730,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>666993310</v>
+        <v>662351109</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>3</v>
@@ -735,55 +738,55 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>690355882</v>
+        <v>756987479</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>681659185</v>
+        <v>749369645</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>634020881</v>
+        <v>728604780</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>565768573</v>
+        <v>653688410</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>572508038</v>
+        <v>675753374</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>567135268</v>
+        <v>173551932</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>735970851</v>
+        <v>692522034</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>3</v>
@@ -791,587 +794,257 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>764443002</v>
+        <v>744524038</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>764132845</v>
+        <v>715151795</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>763137662</v>
+        <v>641360528</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>761928377</v>
+        <v>554167035</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>760673537</v>
+        <v>766288694</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>756013748</v>
+        <v>766238715</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>755988965</v>
+        <v>577832821</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46">
-        <v>755180746</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B46" s="3"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47">
-        <v>727675542</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B47" s="3"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48">
-        <v>638496145</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>703253454</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>637140348</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>597202252</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>595010152</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>570265011</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>556835001</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>552459459</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>173468970</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>169956475</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>612610778</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>623266271</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
-        <v>627864626</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
-        <v>766703403</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
-        <v>753869423</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63">
-        <v>753817703</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64">
-        <v>753383441</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65">
-        <v>712770498</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66">
-        <v>637203369</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67">
-        <v>527888170</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68">
-        <v>741050359</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69">
-        <v>726061983</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70">
-        <v>703003321</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71">
-        <v>699676999</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72">
-        <v>692933496</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73">
-        <v>690544949</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74">
-        <v>670050404</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75">
-        <v>745513881</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76">
-        <v>765062223</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77">
-        <v>763867102</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78">
-        <v>748560236</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79">
-        <v>624190579</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80">
-        <v>607111691</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81">
-        <v>597750417</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82">
-        <v>703853048</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83">
-        <v>701004446</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84">
-        <v>626285773</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85">
-        <v>647262116</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86">
-        <v>655198194</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87">
-        <v>773282342</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88">
-        <v>765894757</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89">
-        <v>755243726</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90">
-        <v>755212929</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91">
-        <v>749347377</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92">
-        <v>716492032</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93">
-        <v>704459852</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94">
-        <v>696827314</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95">
-        <v>683871630</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96">
-        <v>663918237</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97">
-        <v>641028901</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98">
-        <v>623777517</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99">
-        <v>618107571</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100">
-        <v>702745831</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101">
-        <v>770118051</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102">
-        <v>756835165</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103">
-        <v>732897933</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104">
-        <v>640547539</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105">
-        <v>651230520</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106">
-        <v>753964059</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107">
-        <v>724228360</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108">
-        <v>680067166</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109">
-        <v>765359363</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110">
-        <v>764445296</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111">
-        <v>656916867</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B48" s="3"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="3"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="3"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="3"/>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" s="3"/>
@@ -1790,12 +1463,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A156:A279 A112:A154">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46:A68">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A68">
+  <conditionalFormatting sqref="A69:A111">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A69:A111">
+  <conditionalFormatting sqref="A2:A45">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28618"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D464BAE-221B-46D1-B989-171C7DD9E502}"/>
+  <xr:revisionPtr revIDLastSave="606" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48EC7154-9213-427E-A9C5-B1E5F4E2508A}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="6">
   <si>
     <t>Recibo</t>
   </si>
@@ -50,7 +50,10 @@
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t xml:space="preserve">????????                                               </t>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -132,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -145,12 +148,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -498,55 +505,55 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>742207420</v>
+        <v>723603795</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="6">
-        <v>642045151</v>
+      <c r="A3">
+        <v>541539759</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="6">
-        <v>755441163</v>
+      <c r="A4">
+        <v>732316223</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="6">
-        <v>730464975</v>
+      <c r="A5">
+        <v>709381101</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="6">
-        <v>709879740</v>
+      <c r="A6">
+        <v>705584518</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>635221421</v>
+        <v>690119098</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>652918065</v>
+        <v>681385609</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
@@ -554,23 +561,23 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>721974206</v>
+        <v>672886425</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>766224954</v>
+        <v>664456807</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>171478237</v>
+        <v>658827518</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>2</v>
@@ -578,7 +585,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>755523044</v>
+        <v>652426077</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
@@ -586,7 +593,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>724553726</v>
+        <v>647161482</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>2</v>
@@ -594,7 +601,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>744902796</v>
+        <v>644978870</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
@@ -602,7 +609,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>717055432</v>
+        <v>173545033</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
@@ -610,95 +617,95 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>716995406</v>
+        <v>775081403</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>713274276</v>
+        <v>771656224</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>694190038</v>
+        <v>720803331</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>659705705</v>
+        <v>767581451</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>680094053</v>
+        <v>767421641</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>678119615</v>
+        <v>758811867</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>671957771</v>
+        <v>717145902</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>669910824</v>
+        <v>716197417</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>640466789</v>
+        <v>625043512</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>651547469</v>
+        <v>638740187</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>645744727</v>
+        <v>756656256</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>610572319</v>
+        <v>697675472</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>2</v>
@@ -706,7 +713,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>173161492</v>
+        <v>767322922</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>2</v>
@@ -714,147 +721,77 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>670056369</v>
+        <v>767643004</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>670529597</v>
+        <v>767586591</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>662351109</v>
+        <v>756722165</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32">
-        <v>756987479</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>749369645</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>728604780</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>653688410</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>675753374</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>173551932</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>692522034</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>744524038</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>715151795</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>641360528</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>554167035</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>766288694</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>766238715</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>577832821</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="3"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="3"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="3"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="3"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="3"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="3"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="3"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="3"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="3"/>
+    </row>
+    <row r="46" spans="2:2">
       <c r="B46" s="3"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="2:2">
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="2:2">
       <c r="B48" s="3"/>
     </row>
     <row r="49" spans="2:2">
@@ -1463,15 +1400,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A156:A279 A112:A154">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46:A68">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A46:A68">
+  <conditionalFormatting sqref="A69:A111">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A69:A111">
+  <conditionalFormatting sqref="A32:A45">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A45">
+  <conditionalFormatting sqref="A2:A31">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="606" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48EC7154-9213-427E-A9C5-B1E5F4E2508A}"/>
+  <xr:revisionPtr revIDLastSave="610" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7AB6665-7D87-4648-B4B8-9B15C5B4F028}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -47,13 +47,10 @@
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+    <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -505,7 +502,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>723603795</v>
+        <v>724382985</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -513,15 +510,15 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>541539759</v>
+        <v>708260744</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>732316223</v>
+        <v>707888735</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -529,7 +526,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>709381101</v>
+        <v>723488569</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -537,7 +534,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>705584518</v>
+        <v>719972386</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
@@ -545,7 +542,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>690119098</v>
+        <v>716513464</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
@@ -553,7 +550,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>681385609</v>
+        <v>705483935</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
@@ -561,7 +558,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>672886425</v>
+        <v>700914405</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>2</v>
@@ -569,7 +566,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>664456807</v>
+        <v>697644049</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>2</v>
@@ -577,7 +574,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>658827518</v>
+        <v>687218333</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>2</v>
@@ -585,7 +582,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>652426077</v>
+        <v>683464907</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
@@ -593,7 +590,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>647161482</v>
+        <v>680323205</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>2</v>
@@ -601,7 +598,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>644978870</v>
+        <v>677711016</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
@@ -609,7 +606,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>173545033</v>
+        <v>676795507</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
@@ -617,95 +614,95 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>775081403</v>
+        <v>666205053</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>771656224</v>
+        <v>658953090</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>720803331</v>
+        <v>634520492</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>767581451</v>
+        <v>767211620</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>767421641</v>
+        <v>770753048</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>758811867</v>
+        <v>552288684</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>717145902</v>
+        <v>770731135</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>716197417</v>
+        <v>769137633</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>625043512</v>
+        <v>767211612</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>638740187</v>
+        <v>759248200</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>756656256</v>
+        <v>758883619</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>697675472</v>
+        <v>757218858</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>2</v>
@@ -713,7 +710,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>767322922</v>
+        <v>756787655</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>2</v>
@@ -721,7 +718,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>767643004</v>
+        <v>755511593</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>2</v>
@@ -729,69 +726,134 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>767586591</v>
+        <v>691068872</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>756722165</v>
+        <v>639276520</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="B32" s="3"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="3"/>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="3"/>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="2:2">
+      <c r="A32">
+        <v>758015477</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>758001394</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>769711866</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>755913955</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>770935496</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>629613799</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>640037770</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>770961757</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>725920254</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>770327413</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>770628422</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>769369673</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>766126357</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="B45" s="3"/>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="1:2">
       <c r="B46" s="3"/>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="1:2">
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="1:2">
       <c r="B48" s="3"/>
     </row>
     <row r="49" spans="2:2">
@@ -1400,18 +1462,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A156:A279 A112:A154">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:A68">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:A111">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:A45">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A31">
+  <conditionalFormatting sqref="A2:A44">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28627"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28706"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="632" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEAE6570-C098-4CAF-8E58-24A8DA904EE6}"/>
+  <xr:revisionPtr revIDLastSave="651" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F193A3ED-B2B7-45BD-B885-D596D6733AA6}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="7">
   <si>
     <t>Recibo</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">OCORRENCIA_INTERNA                                     </t>
   </si>
   <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t xml:space="preserve">????????                                               </t>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+    <t xml:space="preserve">????????                                               </t>
   </si>
 </sst>
 </file>
@@ -164,13 +164,8 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FFFF0000"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -179,8 +174,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -524,7 +524,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>521504112</v>
+        <v>770398067</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -532,2526 +532,2091 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>765937119</v>
+        <v>668149564</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>744165451</v>
+        <v>772872176</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>725062313</v>
+        <v>772543009</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>711016232</v>
+        <v>748292798</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>699469197</v>
+        <v>773731983</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>686039433</v>
+        <v>731681445</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>682432806</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>2</v>
+        <v>762892960</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>664433319</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>2</v>
+        <v>762911117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>644103768</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>2</v>
+        <v>778294474</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>643740743</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>2</v>
+        <v>775634904</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>585364577</v>
-      </c>
-      <c r="B13" s="3" t="s">
+        <v>774095131</v>
+      </c>
+      <c r="B13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>714202714</v>
-      </c>
-      <c r="B14" s="3" t="s">
+        <v>732112515</v>
+      </c>
+      <c r="B14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>742038726</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>730794827</v>
+      </c>
+      <c r="B15" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>660739420</v>
-      </c>
-      <c r="B16" s="3" t="s">
+        <v>730774514</v>
+      </c>
+      <c r="B16" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>684144326</v>
-      </c>
-      <c r="B17" s="3" t="s">
+        <v>730463209</v>
+      </c>
+      <c r="B17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>700774445</v>
-      </c>
-      <c r="B18" s="3" t="s">
+        <v>729390009</v>
+      </c>
+      <c r="B18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>697257297</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>727926135</v>
+      </c>
+      <c r="B19" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>672684143</v>
-      </c>
-      <c r="B20" s="3" t="s">
+        <v>725966463</v>
+      </c>
+      <c r="B20" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>547285019</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>725416105</v>
+      </c>
+      <c r="B21" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>738477730</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
+        <v>725229631</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>771044967</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
+        <v>725120368</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>594823068</v>
-      </c>
-      <c r="B24" s="3" t="s">
+        <v>724994243</v>
+      </c>
+      <c r="B24" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>677701215</v>
-      </c>
-      <c r="B25" s="3" t="s">
+        <v>724605526</v>
+      </c>
+      <c r="B25" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>727250213</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>723932202</v>
+      </c>
+      <c r="B26" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>773831817</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>2</v>
+        <v>723376384</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>748515297</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>2</v>
+        <v>719459913</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>739445918</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>2</v>
+        <v>716082254</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>735942611</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>2</v>
+        <v>715780734</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>734766052</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>2</v>
+        <v>714832619</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>730340993</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
+        <v>714830753</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>726944006</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
+        <v>713485013</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>724969955</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
+        <v>712137623</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>724969914</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
+        <v>710782446</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>724969864</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
+        <v>710550264</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>723028290</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
+        <v>708962224</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>713375453</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
+        <v>708181023</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>712199151</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
+        <v>707406280</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>710868849</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
+        <v>705514309</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>706689688</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
+        <v>704875610</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>704755143</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
+        <v>704260219</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>694861349</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
+        <v>702175666</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>693758124</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
+        <v>702175658</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>691869394</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
+        <v>702094479</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>691220499</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
+        <v>701626578</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>683861433</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
+        <v>766625895</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>676435054</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
+        <v>766576130</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>669374278</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
+        <v>766193183</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>651413241</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
+        <v>766145324</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>651302204</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
+        <v>766097780</v>
+      </c>
+      <c r="B51" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>647573942</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
+        <v>766038420</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>586980231</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
+        <v>765622083</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>655893224</v>
-      </c>
-      <c r="B54" s="3" t="s">
+        <v>765586460</v>
+      </c>
+      <c r="B54" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>695671499</v>
-      </c>
-      <c r="B55" s="3" t="s">
+        <v>765585652</v>
+      </c>
+      <c r="B55" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>708001171</v>
-      </c>
-      <c r="B56" s="3" t="s">
+        <v>765374065</v>
+      </c>
+      <c r="B56" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>668783032</v>
-      </c>
-      <c r="B57" s="3" t="s">
+        <v>765297357</v>
+      </c>
+      <c r="B57" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>654924681</v>
-      </c>
-      <c r="B58" s="3" t="s">
+        <v>765251123</v>
+      </c>
+      <c r="B58" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>660039334</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
+        <v>764706622</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>557677741</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
+        <v>764688044</v>
+      </c>
+      <c r="B60" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>740362599</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>2</v>
+        <v>764668939</v>
+      </c>
+      <c r="B61" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>642630002</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>2</v>
+        <v>764628966</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>667916930</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>2</v>
+        <v>764622092</v>
+      </c>
+      <c r="B63" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>740909886</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>2</v>
+        <v>764577205</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>732118157</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>2</v>
+        <v>764425728</v>
+      </c>
+      <c r="B65" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>616771162</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>2</v>
+        <v>764374629</v>
+      </c>
+      <c r="B66" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>576362069</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>4</v>
+        <v>764196162</v>
+      </c>
+      <c r="B67" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>759305182</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>5</v>
+        <v>764064980</v>
+      </c>
+      <c r="B68" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>736056023</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>5</v>
+        <v>764005959</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>731862870</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>5</v>
+        <v>763769894</v>
+      </c>
+      <c r="B70" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>669451985</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>5</v>
+        <v>763632811</v>
+      </c>
+      <c r="B71" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>645909908</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>5</v>
+        <v>763343260</v>
+      </c>
+      <c r="B72" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>618129609</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>5</v>
+        <v>763300997</v>
+      </c>
+      <c r="B73" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>598877151</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>5</v>
+        <v>763138678</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>598417602</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>5</v>
+        <v>762892952</v>
+      </c>
+      <c r="B75" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>694203567</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>4</v>
+        <v>762856684</v>
+      </c>
+      <c r="B76" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>737228332</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>4</v>
+        <v>762799272</v>
+      </c>
+      <c r="B77" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>772518571</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>2</v>
+        <v>762526618</v>
+      </c>
+      <c r="B78" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>661983365</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>2</v>
+        <v>762292559</v>
+      </c>
+      <c r="B79" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>636617007</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>2</v>
+        <v>762251019</v>
+      </c>
+      <c r="B80" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>665885186</v>
-      </c>
-      <c r="B81" s="3" t="s">
+        <v>760706535</v>
+      </c>
+      <c r="B81" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>702566559</v>
-      </c>
-      <c r="B82" s="3" t="s">
+        <v>760704084</v>
+      </c>
+      <c r="B82" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>674393412</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>2</v>
+        <v>759556081</v>
+      </c>
+      <c r="B83" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>567501006</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>2</v>
+        <v>758661692</v>
+      </c>
+      <c r="B84" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>607192014</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>2</v>
+        <v>758408466</v>
+      </c>
+      <c r="B85" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>593726825</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>2</v>
+        <v>758040822</v>
+      </c>
+      <c r="B86" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>590612408</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>2</v>
+        <v>743295648</v>
+      </c>
+      <c r="B87" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>582514240</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>2</v>
+        <v>738430424</v>
+      </c>
+      <c r="B88" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>579640057</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>2</v>
+        <v>737116271</v>
+      </c>
+      <c r="B89" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>567500990</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>2</v>
+        <v>737040034</v>
+      </c>
+      <c r="B90" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>668821287</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>2</v>
+        <v>736783477</v>
+      </c>
+      <c r="B91" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>740149855</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>2</v>
+        <v>736762182</v>
+      </c>
+      <c r="B92" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>732003201</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>2</v>
+        <v>735585816</v>
+      </c>
+      <c r="B93" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>174657597</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>2</v>
+        <v>735357430</v>
+      </c>
+      <c r="B94" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>778055594</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>2</v>
+        <v>734546728</v>
+      </c>
+      <c r="B95" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>768036596</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>2</v>
+        <v>733500239</v>
+      </c>
+      <c r="B96" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>751671086</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>2</v>
+        <v>733387116</v>
+      </c>
+      <c r="B97" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>533850826</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>2</v>
+        <v>733196285</v>
+      </c>
+      <c r="B98" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>720731979</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>2</v>
+        <v>732197557</v>
+      </c>
+      <c r="B99" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>706832916</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>2</v>
+        <v>732163336</v>
+      </c>
+      <c r="B100" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>691260354</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>2</v>
+        <v>742716792</v>
+      </c>
+      <c r="B101" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102">
-        <v>640119065</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>2</v>
+        <v>741514420</v>
+      </c>
+      <c r="B102" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103">
-        <v>622078545</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>2</v>
+        <v>741009314</v>
+      </c>
+      <c r="B103" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104">
-        <v>621889959</v>
-      </c>
-      <c r="B104" s="3" t="s">
+        <v>740657121</v>
+      </c>
+      <c r="B104" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105">
-        <v>618667442</v>
-      </c>
-      <c r="B105" s="3" t="s">
+        <v>740114032</v>
+      </c>
+      <c r="B105" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106">
-        <v>595522370</v>
-      </c>
-      <c r="B106" s="3" t="s">
+        <v>740005263</v>
+      </c>
+      <c r="B106" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107">
-        <v>583232347</v>
-      </c>
-      <c r="B107" s="3" t="s">
+        <v>739908329</v>
+      </c>
+      <c r="B107" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108">
-        <v>568153195</v>
-      </c>
-      <c r="B108" s="3" t="s">
+        <v>739631533</v>
+      </c>
+      <c r="B108" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109">
-        <v>780740282</v>
-      </c>
-      <c r="B109" s="3" t="s">
+        <v>738653074</v>
+      </c>
+      <c r="B109" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110">
-        <v>775252095</v>
-      </c>
-      <c r="B110" s="3" t="s">
+        <v>699497305</v>
+      </c>
+      <c r="B110" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111">
-        <v>744904230</v>
-      </c>
-      <c r="B111" s="3" t="s">
+        <v>696864424</v>
+      </c>
+      <c r="B111" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112">
-        <v>772020719</v>
-      </c>
-      <c r="B112" s="3" t="s">
+        <v>696819295</v>
+      </c>
+      <c r="B112" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113">
-        <v>767806791</v>
-      </c>
-      <c r="B113" s="3" t="s">
+        <v>695826044</v>
+      </c>
+      <c r="B113" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114">
-        <v>759118767</v>
-      </c>
-      <c r="B114" s="3" t="s">
+        <v>694419890</v>
+      </c>
+      <c r="B114" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115">
-        <v>728621883</v>
-      </c>
-      <c r="B115" s="3" t="s">
+        <v>694397419</v>
+      </c>
+      <c r="B115" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116">
-        <v>736872577</v>
-      </c>
-      <c r="B116" s="3" t="s">
+        <v>693725529</v>
+      </c>
+      <c r="B116" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117">
-        <v>727717872</v>
-      </c>
-      <c r="B117" s="3" t="s">
+        <v>693392395</v>
+      </c>
+      <c r="B117" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118">
-        <v>723387670</v>
-      </c>
-      <c r="B118" s="3" t="s">
+        <v>693346128</v>
+      </c>
+      <c r="B118" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119">
-        <v>720710148</v>
-      </c>
-      <c r="B119" s="3" t="s">
+        <v>692852464</v>
+      </c>
+      <c r="B119" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120">
-        <v>719632337</v>
-      </c>
-      <c r="B120" s="3" t="s">
+        <v>691825396</v>
+      </c>
+      <c r="B120" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121">
-        <v>715211086</v>
-      </c>
-      <c r="B121" s="3" t="s">
+        <v>690447226</v>
+      </c>
+      <c r="B121" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122">
-        <v>712982630</v>
-      </c>
-      <c r="B122" s="3" t="s">
+        <v>689525610</v>
+      </c>
+      <c r="B122" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123">
-        <v>709991701</v>
-      </c>
-      <c r="B123" s="3" t="s">
+        <v>687946750</v>
+      </c>
+      <c r="B123" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124">
-        <v>705801086</v>
-      </c>
-      <c r="B124" s="3" t="s">
+        <v>687750590</v>
+      </c>
+      <c r="B124" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125">
-        <v>705150468</v>
-      </c>
-      <c r="B125" s="3" t="s">
+        <v>685175014</v>
+      </c>
+      <c r="B125" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126">
-        <v>697808115</v>
-      </c>
-      <c r="B126" s="3" t="s">
+        <v>684622917</v>
+      </c>
+      <c r="B126" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127">
-        <v>667660447</v>
-      </c>
-      <c r="B127" s="3" t="s">
+        <v>684608015</v>
+      </c>
+      <c r="B127" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128">
-        <v>689381071</v>
-      </c>
-      <c r="B128" s="3" t="s">
+        <v>682814680</v>
+      </c>
+      <c r="B128" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129">
-        <v>689102329</v>
-      </c>
-      <c r="B129" s="3" t="s">
+        <v>682182450</v>
+      </c>
+      <c r="B129" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130">
-        <v>667082758</v>
-      </c>
-      <c r="B130" s="3" t="s">
+        <v>682004902</v>
+      </c>
+      <c r="B130" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131">
-        <v>647589120</v>
-      </c>
-      <c r="B131" s="3" t="s">
+        <v>681645911</v>
+      </c>
+      <c r="B131" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132">
-        <v>644783700</v>
-      </c>
-      <c r="B132" s="3" t="s">
+        <v>680298308</v>
+      </c>
+      <c r="B132" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133">
-        <v>666266261</v>
-      </c>
-      <c r="B133" s="3" t="s">
+        <v>679868061</v>
+      </c>
+      <c r="B133" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134">
-        <v>665196766</v>
-      </c>
-      <c r="B134" s="3" t="s">
+        <v>676876091</v>
+      </c>
+      <c r="B134" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135">
-        <v>717901098</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>4</v>
+        <v>674781004</v>
+      </c>
+      <c r="B135" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136">
-        <v>691636983</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>4</v>
+        <v>673650846</v>
+      </c>
+      <c r="B136" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137">
-        <v>738899156</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>6</v>
+        <v>672958216</v>
+      </c>
+      <c r="B137" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138">
-        <v>624036905</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>2</v>
+        <v>672474404</v>
+      </c>
+      <c r="B138" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139">
-        <v>644665881</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>2</v>
+        <v>669910097</v>
+      </c>
+      <c r="B139" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140">
-        <v>709261113</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>2</v>
+        <v>664125139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141">
-        <v>771696626</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>2</v>
+        <v>664084153</v>
+      </c>
+      <c r="B141" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142">
-        <v>580740102</v>
-      </c>
-      <c r="B142" s="3" t="s">
+        <v>663770117</v>
+      </c>
+      <c r="B142" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143">
-        <v>777758453</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>2</v>
+        <v>661309314</v>
+      </c>
+      <c r="B143" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144">
-        <v>592888493</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>2</v>
+        <v>658991066</v>
+      </c>
+      <c r="B144" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145">
-        <v>598308322</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>2</v>
+        <v>655476848</v>
+      </c>
+      <c r="B145" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146">
-        <v>715036525</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>2</v>
+        <v>654530884</v>
+      </c>
+      <c r="B146" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147">
-        <v>723021592</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>2</v>
+        <v>649315276</v>
+      </c>
+      <c r="B147" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148">
-        <v>722992249</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>2</v>
+        <v>649315268</v>
+      </c>
+      <c r="B148" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149">
-        <v>670153950</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>2</v>
+        <v>646958664</v>
+      </c>
+      <c r="B149" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150">
-        <v>657712752</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>2</v>
+        <v>645277371</v>
+      </c>
+      <c r="B150" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151">
-        <v>620466692</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>2</v>
+        <v>644997466</v>
+      </c>
+      <c r="B151" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152">
-        <v>747388118</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>2</v>
+        <v>644997458</v>
+      </c>
+      <c r="B152" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153">
-        <v>683160992</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>2</v>
+        <v>644933107</v>
+      </c>
+      <c r="B153" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154">
-        <v>752840953</v>
-      </c>
-      <c r="B154" s="3" t="s">
+        <v>643961612</v>
+      </c>
+      <c r="B154" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155">
-        <v>775245867</v>
-      </c>
-      <c r="B155" s="3" t="s">
+        <v>640066720</v>
+      </c>
+      <c r="B155" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156">
-        <v>690059070</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>2</v>
+        <v>635912698</v>
+      </c>
+      <c r="B156" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157">
-        <v>718282175</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>2</v>
+        <v>635446051</v>
+      </c>
+      <c r="B157" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158">
-        <v>717140572</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>2</v>
+        <v>630510414</v>
+      </c>
+      <c r="B158" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159">
-        <v>715625814</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>2</v>
+        <v>626966711</v>
+      </c>
+      <c r="B159" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160">
-        <v>710868005</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>2</v>
+        <v>625832781</v>
+      </c>
+      <c r="B160" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161">
-        <v>709723765</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>2</v>
+        <v>623280850</v>
+      </c>
+      <c r="B161" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162">
-        <v>709717726</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>2</v>
+        <v>618335263</v>
+      </c>
+      <c r="B162" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163">
-        <v>703143432</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>2</v>
+        <v>616112912</v>
+      </c>
+      <c r="B163" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164">
-        <v>701126223</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>2</v>
+        <v>613885544</v>
+      </c>
+      <c r="B164" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165">
-        <v>699828525</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>2</v>
+        <v>609167386</v>
+      </c>
+      <c r="B165" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166">
-        <v>688937683</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>2</v>
+        <v>607571142</v>
+      </c>
+      <c r="B166" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167">
-        <v>683542256</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>2</v>
+        <v>588272280</v>
+      </c>
+      <c r="B167" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168">
-        <v>680628504</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>2</v>
+        <v>576022572</v>
+      </c>
+      <c r="B168" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169">
-        <v>677855631</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>2</v>
+        <v>573735705</v>
+      </c>
+      <c r="B169" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170">
-        <v>677397014</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>2</v>
+        <v>573495870</v>
+      </c>
+      <c r="B170" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171">
-        <v>674361591</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>2</v>
+        <v>571502255</v>
+      </c>
+      <c r="B171" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172">
-        <v>646582233</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>2</v>
+        <v>569777604</v>
+      </c>
+      <c r="B172" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173">
-        <v>645405345</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>2</v>
+        <v>563172216</v>
+      </c>
+      <c r="B173" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174">
-        <v>623539958</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>2</v>
+        <v>550514917</v>
+      </c>
+      <c r="B174" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175">
-        <v>609779453</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>2</v>
+        <v>548650310</v>
+      </c>
+      <c r="B175" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176">
-        <v>609678689</v>
-      </c>
-      <c r="B176" s="3" t="s">
+        <v>777833298</v>
+      </c>
+      <c r="B176" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177">
-        <v>609330430</v>
-      </c>
-      <c r="B177" s="3" t="s">
+        <v>778825566</v>
+      </c>
+      <c r="B177" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178">
-        <v>595232491</v>
-      </c>
-      <c r="B178" s="3" t="s">
+        <v>775112943</v>
+      </c>
+      <c r="B178" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179">
-        <v>589125701</v>
-      </c>
-      <c r="B179" s="3" t="s">
+        <v>768063673</v>
+      </c>
+      <c r="B179" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180">
-        <v>586218657</v>
-      </c>
-      <c r="B180" s="3" t="s">
+        <v>689768749</v>
+      </c>
+      <c r="B180" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181">
-        <v>664801051</v>
-      </c>
-      <c r="B181" s="3" t="s">
+        <v>739290819</v>
+      </c>
+      <c r="B181" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182">
-        <v>774213106</v>
-      </c>
-      <c r="B182" s="3" t="s">
+        <v>733573624</v>
+      </c>
+      <c r="B182" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183">
-        <v>579481783</v>
-      </c>
-      <c r="B183" s="3" t="s">
+        <v>735758488</v>
+      </c>
+      <c r="B183" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184">
-        <v>573270281</v>
-      </c>
-      <c r="B184" s="3" t="s">
+        <v>738610850</v>
+      </c>
+      <c r="B184" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185">
-        <v>562784219</v>
-      </c>
-      <c r="B185" s="3" t="s">
+        <v>755148032</v>
+      </c>
+      <c r="B185" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186">
-        <v>530754112</v>
-      </c>
-      <c r="B186" s="3" t="s">
+        <v>745767834</v>
+      </c>
+      <c r="B186" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187">
-        <v>528884632</v>
-      </c>
-      <c r="B187" s="3" t="s">
+        <v>640439364</v>
+      </c>
+      <c r="B187" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188">
-        <v>528884624</v>
-      </c>
-      <c r="B188" s="3" t="s">
+        <v>668349487</v>
+      </c>
+      <c r="B188" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189">
-        <v>174658595</v>
-      </c>
-      <c r="B189" s="3" t="s">
+        <v>643427283</v>
+      </c>
+      <c r="B189" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190">
-        <v>176288334</v>
-      </c>
-      <c r="B190" s="3" t="s">
+        <v>571524382</v>
+      </c>
+      <c r="B190" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191">
-        <v>175813868</v>
-      </c>
-      <c r="B191" s="3" t="s">
+        <v>599356148</v>
+      </c>
+      <c r="B191" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192">
-        <v>760680490</v>
-      </c>
-      <c r="B192" s="3" t="s">
+        <v>597144306</v>
+      </c>
+      <c r="B192" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193">
-        <v>748400169</v>
-      </c>
-      <c r="B193" s="3" t="s">
+        <v>592058642</v>
+      </c>
+      <c r="B193" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194">
-        <v>745397723</v>
-      </c>
-      <c r="B194" s="3" t="s">
+        <v>589520950</v>
+      </c>
+      <c r="B194" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195">
-        <v>745165286</v>
-      </c>
-      <c r="B195" s="3" t="s">
+        <v>588518849</v>
+      </c>
+      <c r="B195" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196">
-        <v>742343654</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>2</v>
+        <v>579074679</v>
+      </c>
+      <c r="B196" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197">
-        <v>740121797</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>2</v>
+        <v>773491901</v>
+      </c>
+      <c r="B197" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198">
-        <v>737612311</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>2</v>
+        <v>767164092</v>
+      </c>
+      <c r="B198" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199">
-        <v>736488747</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>2</v>
+        <v>767002771</v>
+      </c>
+      <c r="B199" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200">
-        <v>734734654</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>2</v>
+        <v>678727789</v>
+      </c>
+      <c r="B200" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201">
-        <v>733976611</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>2</v>
+        <v>590640821</v>
+      </c>
+      <c r="B201" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202">
-        <v>726931516</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>2</v>
+        <v>618778744</v>
+      </c>
+      <c r="B202" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203">
-        <v>724945120</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>2</v>
+        <v>778592984</v>
+      </c>
+      <c r="B203" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204">
-        <v>723252486</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>2</v>
+        <v>740695139</v>
+      </c>
+      <c r="B204" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205">
-        <v>722458852</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>2</v>
+        <v>703533426</v>
+      </c>
+      <c r="B205" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206">
-        <v>720577760</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>2</v>
+        <v>710738075</v>
+      </c>
+      <c r="B206" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207">
-        <v>764347336</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>2</v>
+        <v>579998018</v>
+      </c>
+      <c r="B207" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208">
-        <v>764328641</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>2</v>
+        <v>778426399</v>
+      </c>
+      <c r="B208" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209">
-        <v>764011981</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>2</v>
+        <v>726175734</v>
+      </c>
+      <c r="B209" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210">
-        <v>763609876</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>2</v>
+        <v>707225045</v>
+      </c>
+      <c r="B210" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211">
-        <v>762862971</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>2</v>
+        <v>777453394</v>
+      </c>
+      <c r="B211" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212">
-        <v>762224354</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>2</v>
+        <v>760924021</v>
+      </c>
+      <c r="B212" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213">
-        <v>762038085</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>2</v>
+        <v>684780491</v>
+      </c>
+      <c r="B213" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214">
-        <v>761453228</v>
-      </c>
-      <c r="B214" s="3" t="s">
+        <v>700254406</v>
+      </c>
+      <c r="B214" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215">
-        <v>761328883</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>2</v>
+        <v>726608338</v>
+      </c>
+      <c r="B215" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216">
-        <v>760675052</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>2</v>
+        <v>738931009</v>
+      </c>
+      <c r="B216" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217">
-        <v>752544712</v>
-      </c>
-      <c r="B217" s="3" t="s">
+        <v>686437975</v>
+      </c>
+      <c r="B217" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218">
-        <v>575340223</v>
-      </c>
-      <c r="B218" s="3" t="s">
+        <v>664427931</v>
+      </c>
+      <c r="B218" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219">
-        <v>574577239</v>
+        <v>579830302</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220">
-        <v>749500231</v>
+        <v>578660700</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221">
-        <v>751931142</v>
+        <v>670249568</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222">
-        <v>662128085</v>
+        <v>732430164</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223">
-        <v>593763398</v>
+        <v>672531104</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224">
-        <v>617551951</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>3</v>
+        <v>603356704</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225">
-        <v>634672558</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>3</v>
+        <v>624159970</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226">
-        <v>633681774</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>3</v>
+        <v>627178902</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227">
-        <v>672270588</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>3</v>
+        <v>627461076</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228">
-        <v>696255995</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>3</v>
+        <v>719831285</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229">
-        <v>706761537</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>3</v>
+        <v>742808466</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230">
-        <v>691523710</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B230" s="3"/>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231">
-        <v>683483089</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B231" s="3"/>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232">
-        <v>765603562</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B232" s="3"/>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233">
-        <v>761323843</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B233" s="3"/>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234">
-        <v>603040191</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B234" s="3"/>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235">
-        <v>745463640</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B235" s="3"/>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236">
-        <v>741893600</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B236" s="3"/>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237">
-        <v>679218754</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B237" s="3"/>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238">
-        <v>711030852</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B238" s="3"/>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239">
-        <v>690624592</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B239" s="3"/>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240">
-        <v>689229395</v>
-      </c>
-      <c r="B240" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2">
-      <c r="A241">
-        <v>768271441</v>
-      </c>
-      <c r="B241" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2">
-      <c r="A242">
-        <v>745104533</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
-      <c r="A243">
-        <v>724265693</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2">
-      <c r="A244">
-        <v>715258483</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2">
-      <c r="A245">
-        <v>620717375</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2">
-      <c r="A246">
-        <v>719640082</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2">
-      <c r="A247">
-        <v>710442777</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2">
-      <c r="A248">
-        <v>637195987</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2">
-      <c r="A249">
-        <v>694934310</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2">
-      <c r="A250">
-        <v>774839066</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2">
-      <c r="A251">
-        <v>774539641</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2">
-      <c r="A252">
-        <v>725870806</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2">
-      <c r="A253">
-        <v>735892840</v>
-      </c>
-      <c r="B253" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2">
-      <c r="A254">
-        <v>689976318</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2">
-      <c r="A255">
-        <v>775891546</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2">
-      <c r="A256">
-        <v>573697509</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2">
-      <c r="A257">
-        <v>719791398</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2">
-      <c r="A258">
-        <v>657091959</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2">
-      <c r="A259">
-        <v>609890607</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2">
-      <c r="A260">
-        <v>677745501</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2">
-      <c r="A261">
-        <v>774856235</v>
-      </c>
-      <c r="B261" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2">
-      <c r="A262">
-        <v>774012128</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2">
-      <c r="A263">
-        <v>702161526</v>
-      </c>
-      <c r="B263" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2">
-      <c r="A264">
-        <v>701282208</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2">
-      <c r="A265">
-        <v>619663176</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
-      <c r="A266">
-        <v>637058417</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
-      <c r="A267">
-        <v>619628013</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
-      <c r="A268">
-        <v>698860909</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2">
-      <c r="A269">
-        <v>683021277</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2">
-      <c r="A270">
-        <v>690342997</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2">
-      <c r="A271">
-        <v>776409009</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2">
-      <c r="A272">
-        <v>577449592</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2">
-      <c r="A273">
-        <v>561319165</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2">
-      <c r="A274">
-        <v>733825479</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2">
-      <c r="A275">
-        <v>751246749</v>
-      </c>
-      <c r="B275" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2">
-      <c r="A276">
-        <v>734899374</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2">
-      <c r="A277">
-        <v>634136976</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2">
-      <c r="A278">
-        <v>629904594</v>
-      </c>
-      <c r="B278" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2">
-      <c r="A279">
-        <v>623262213</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2">
-      <c r="A280">
-        <v>580341174</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2">
-      <c r="A281">
-        <v>592201515</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2">
-      <c r="A282">
-        <v>740263193</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2">
-      <c r="A283">
-        <v>733534485</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2">
-      <c r="A284">
-        <v>723723619</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2">
-      <c r="A285">
-        <v>720681877</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2">
-      <c r="A286">
-        <v>688743594</v>
-      </c>
-      <c r="B286" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2">
-      <c r="A287">
-        <v>708877232</v>
-      </c>
-      <c r="B287" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2">
-      <c r="A288">
-        <v>716649235</v>
-      </c>
-      <c r="B288" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2">
-      <c r="A289">
-        <v>712358864</v>
-      </c>
-      <c r="B289" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="A290">
-        <v>714996950</v>
-      </c>
-      <c r="B290" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291">
-        <v>714163635</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2">
-      <c r="A292">
-        <v>707554162</v>
-      </c>
-      <c r="B292" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
-      <c r="A293">
-        <v>680141805</v>
-      </c>
-      <c r="B293" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
-      <c r="A294">
-        <v>680607847</v>
-      </c>
-      <c r="B294" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
-      <c r="A295">
-        <v>675900538</v>
-      </c>
-      <c r="B295" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2">
-      <c r="A296">
-        <v>675625622</v>
-      </c>
-      <c r="B296" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2">
-      <c r="A297">
-        <v>675597425</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
-      <c r="A298">
-        <v>647894546</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2">
-      <c r="A299">
-        <v>657199232</v>
-      </c>
-      <c r="B299" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
-      <c r="A300">
-        <v>664002882</v>
-      </c>
-      <c r="B300" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
-      <c r="A301">
-        <v>662688757</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2">
-      <c r="A302">
-        <v>660828249</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2">
-      <c r="A303">
-        <v>654091473</v>
-      </c>
-      <c r="B303" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2">
-      <c r="A304">
-        <v>656453481</v>
-      </c>
-      <c r="B304" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2">
-      <c r="A305">
-        <v>776788865</v>
-      </c>
-      <c r="B305" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2">
-      <c r="A306">
-        <v>175799935</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2">
-      <c r="A307">
-        <v>776743092</v>
-      </c>
-      <c r="B307" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2">
-      <c r="A308">
-        <v>759554987</v>
-      </c>
-      <c r="B308" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="309" spans="1:2">
-      <c r="A309">
-        <v>757352871</v>
-      </c>
-      <c r="B309" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="310" spans="1:2">
-      <c r="A310">
-        <v>754305088</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="311" spans="1:2">
-      <c r="A311">
-        <v>655555658</v>
-      </c>
-      <c r="B311" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2">
-      <c r="A312">
-        <v>687471643</v>
-      </c>
-      <c r="B312" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="313" spans="1:2">
-      <c r="A313">
-        <v>704126915</v>
-      </c>
-      <c r="B313" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="314" spans="1:2">
-      <c r="A314">
-        <v>654795396</v>
-      </c>
-      <c r="B314" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="A315">
-        <v>773976810</v>
-      </c>
-      <c r="B315" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2">
-      <c r="A316">
-        <v>636529061</v>
-      </c>
-      <c r="B316" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2">
+      <c r="B240" s="3"/>
+    </row>
+    <row r="241" spans="2:2">
+      <c r="B241" s="3"/>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242" s="3"/>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" s="3"/>
+    </row>
+    <row r="244" spans="2:2">
+      <c r="B244" s="3"/>
+    </row>
+    <row r="245" spans="2:2">
+      <c r="B245" s="3"/>
+    </row>
+    <row r="246" spans="2:2">
+      <c r="B246" s="3"/>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247" s="3"/>
+    </row>
+    <row r="248" spans="2:2">
+      <c r="B248" s="3"/>
+    </row>
+    <row r="249" spans="2:2">
+      <c r="B249" s="3"/>
+    </row>
+    <row r="250" spans="2:2">
+      <c r="B250" s="3"/>
+    </row>
+    <row r="251" spans="2:2">
+      <c r="B251" s="3"/>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252" s="3"/>
+    </row>
+    <row r="253" spans="2:2">
+      <c r="B253" s="3"/>
+    </row>
+    <row r="254" spans="2:2">
+      <c r="B254" s="3"/>
+    </row>
+    <row r="255" spans="2:2">
+      <c r="B255" s="3"/>
+    </row>
+    <row r="256" spans="2:2">
+      <c r="B256" s="3"/>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257" s="3"/>
+    </row>
+    <row r="258" spans="2:2">
+      <c r="B258" s="3"/>
+    </row>
+    <row r="259" spans="2:2">
+      <c r="B259" s="3"/>
+    </row>
+    <row r="260" spans="2:2">
+      <c r="B260" s="3"/>
+    </row>
+    <row r="261" spans="2:2">
+      <c r="B261" s="3"/>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262" s="3"/>
+    </row>
+    <row r="263" spans="2:2">
+      <c r="B263" s="3"/>
+    </row>
+    <row r="264" spans="2:2">
+      <c r="B264" s="3"/>
+    </row>
+    <row r="265" spans="2:2">
+      <c r="B265" s="3"/>
+    </row>
+    <row r="266" spans="2:2">
+      <c r="B266" s="3"/>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267" s="3"/>
+    </row>
+    <row r="268" spans="2:2">
+      <c r="B268" s="3"/>
+    </row>
+    <row r="269" spans="2:2">
+      <c r="B269" s="3"/>
+    </row>
+    <row r="270" spans="2:2">
+      <c r="B270" s="3"/>
+    </row>
+    <row r="271" spans="2:2">
+      <c r="B271" s="3"/>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272" s="3"/>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" s="3"/>
+    </row>
+    <row r="274" spans="2:2">
+      <c r="B274" s="3"/>
+    </row>
+    <row r="275" spans="2:2">
+      <c r="B275" s="3"/>
+    </row>
+    <row r="276" spans="2:2">
+      <c r="B276" s="3"/>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277" s="3"/>
+    </row>
+    <row r="278" spans="2:2">
+      <c r="B278" s="3"/>
+    </row>
+    <row r="279" spans="2:2">
+      <c r="B279" s="3"/>
+    </row>
+    <row r="280" spans="2:2">
+      <c r="B280" s="3"/>
+    </row>
+    <row r="281" spans="2:2">
+      <c r="B281" s="3"/>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" s="3"/>
+    </row>
+    <row r="283" spans="2:2">
+      <c r="B283" s="3"/>
+    </row>
+    <row r="284" spans="2:2">
+      <c r="B284" s="3"/>
+    </row>
+    <row r="285" spans="2:2">
+      <c r="B285" s="3"/>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" s="3"/>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287" s="3"/>
+    </row>
+    <row r="288" spans="2:2">
+      <c r="B288" s="3"/>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" s="3"/>
+    </row>
+    <row r="290" spans="2:2">
+      <c r="B290" s="3"/>
+    </row>
+    <row r="291" spans="2:2">
+      <c r="B291" s="3"/>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292" s="3"/>
+    </row>
+    <row r="293" spans="2:2">
+      <c r="B293" s="3"/>
+    </row>
+    <row r="294" spans="2:2">
+      <c r="B294" s="3"/>
+    </row>
+    <row r="295" spans="2:2">
+      <c r="B295" s="3"/>
+    </row>
+    <row r="296" spans="2:2">
+      <c r="B296" s="3"/>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297" s="3"/>
+    </row>
+    <row r="298" spans="2:2">
+      <c r="B298" s="3"/>
+    </row>
+    <row r="299" spans="2:2">
+      <c r="B299" s="3"/>
+    </row>
+    <row r="300" spans="2:2">
+      <c r="B300" s="3"/>
+    </row>
+    <row r="301" spans="2:2">
+      <c r="B301" s="3"/>
+    </row>
+    <row r="302" spans="2:2">
+      <c r="B302" s="3"/>
+    </row>
+    <row r="303" spans="2:2">
+      <c r="B303" s="3"/>
+    </row>
+    <row r="304" spans="2:2">
+      <c r="B304" s="3"/>
+    </row>
+    <row r="305" spans="2:2">
+      <c r="B305" s="3"/>
+    </row>
+    <row r="306" spans="2:2">
+      <c r="B306" s="3"/>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307" s="3"/>
+    </row>
+    <row r="308" spans="2:2">
+      <c r="B308" s="3"/>
+    </row>
+    <row r="309" spans="2:2">
+      <c r="B309" s="3"/>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" s="3"/>
+    </row>
+    <row r="311" spans="2:2">
+      <c r="B311" s="3"/>
+    </row>
+    <row r="312" spans="2:2">
+      <c r="B312" s="3"/>
+    </row>
+    <row r="313" spans="2:2">
+      <c r="B313" s="3"/>
+    </row>
+    <row r="314" spans="2:2">
+      <c r="B314" s="3"/>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" s="3"/>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" s="3"/>
+    </row>
+    <row r="317" spans="2:2">
       <c r="B317" s="3"/>
     </row>
-    <row r="318" spans="1:2">
+    <row r="318" spans="2:2">
       <c r="B318" s="3"/>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" spans="2:2">
       <c r="B319" s="3"/>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" spans="2:2">
       <c r="B320" s="3"/>
     </row>
     <row r="321" spans="2:2">
@@ -6656,25 +6221,25 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A317:A1192">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1193:A1361">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1362:A1529">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A83">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="A1 A230:A1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A84:A151">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="A230:A316">
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="A2:A218">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A152:A316">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="A219:A229">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B630BF8-99E7-47BE-8A66-D6C9B8C40181}"/>
+  <xr:revisionPtr revIDLastSave="684" documentId="13_ncr:1_{2FE9DAA0-0CD9-422E-B235-F9FF032BE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27B253D0-7E8C-4BB0-A74F-FDF7175C6C15}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -528,7 +528,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>773144872</v>
+        <v>765211317</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -536,7 +536,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>598694515</v>
+        <v>786953301</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -544,146 +544,282 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>585330958</v>
+        <v>682535566</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>771732231</v>
+        <v>701607974</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>724603224</v>
+        <v>678853940</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>677671301</v>
+        <v>676481215</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>677499687</v>
+        <v>665827212</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>661051262</v>
+        <v>786868301</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>724623925</v>
+        <v>655465783</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>783696713</v>
+        <v>176893760</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>606764276</v>
+        <v>798117523</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>581963851</v>
+        <v>759425527</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>746538895</v>
+        <v>767248788</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>734154630</v>
+        <v>759425402</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>698846064</v>
+        <v>727821187</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>680876574</v>
+        <v>723525436</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>737522395</v>
+        <v>744545561</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>727899209</v>
+        <v>665404673</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>784801130</v>
+        <v>672999996</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>772568956</v>
+        <v>656034414</v>
       </c>
       <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>794919229</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>625978147</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>606507683</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>794883391</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>794883383</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>788524019</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>765902162</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>733547123</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>717367985</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>650218922</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>650218914</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>699498576</v>
+      </c>
+      <c r="B33" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>784416244</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>675424661</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>693427977</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>693427969</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>755905209</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="2:2">
@@ -4603,30 +4739,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A650:A1192">
-    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1193:A1361">
-    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1362:A1529">
-    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1 A650:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A214:A580">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A581:A649">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A71:A213">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A70">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A39:A70">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A38">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BFA6F0-979E-4B77-866C-6DFCB46E1682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB5CF04-18C8-4263-BFA6-B7921410C124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="6">
   <si>
     <t>Recibo</t>
   </si>
@@ -47,7 +47,13 @@
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
 </sst>
 </file>
@@ -147,27 +153,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -197,6 +183,21 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -508,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
-  <dimension ref="A1:B1458"/>
+  <dimension ref="A1:B1418"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -525,31 +526,31 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>765203215</v>
+        <v>716322825</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>772097089</v>
+        <v>677644746</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>772281022</v>
+        <v>662129513</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>750092235</v>
+        <v>753922255</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -557,7 +558,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>724605542</v>
+        <v>591119882</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -565,7 +566,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>723311753</v>
+        <v>794794556</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -573,7 +574,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>719417986</v>
+        <v>796299497</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -581,47 +582,47 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>709919942</v>
+        <v>606356776</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>707699975</v>
+        <v>645975594</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>706451022</v>
+        <v>619010758</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>661155238</v>
+        <v>593227220</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>598860363</v>
+        <v>759141025</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>807309756</v>
+        <v>790905115</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -629,7 +630,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>802683395</v>
+        <v>773161934</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -637,7 +638,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>799255181</v>
+        <v>784242913</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -645,7 +646,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>788038002</v>
+        <v>785053350</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -653,7 +654,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>691216505</v>
+        <v>784240016</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -661,7 +662,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>760609408</v>
+        <v>762892788</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -669,7 +670,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>787563604</v>
+        <v>710113881</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -677,7 +678,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>621654569</v>
+        <v>689098790</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -685,15 +686,15 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>765942150</v>
+        <v>691612935</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>799617943</v>
+        <v>726478526</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -701,7 +702,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>641910496</v>
+        <v>741088979</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -709,7 +710,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>797453606</v>
+        <v>740461193</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -717,15 +718,15 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>723369116</v>
+        <v>727992970</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>761804172</v>
+        <v>805185687</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -733,7 +734,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>704522519</v>
+        <v>805964784</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -741,7 +742,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>617377381</v>
+        <v>797058355</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -749,7 +750,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>599769332</v>
+        <v>796272528</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -757,7 +758,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>782338465</v>
+        <v>795791072</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -765,12 +766,270 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>648072712</v>
+        <v>795823834</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>598149270</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>569285442</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>760680607</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>727948105</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>794227524</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>785641246</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>629772264</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>646521967</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>578966610</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>744042650</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>794525984</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>794480404</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>761866908</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>789437864</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>603528773</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>748371055</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="5"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114" s="5"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" s="5"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116" s="5"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117" s="5"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118" s="5"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="3"/>
+    </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B148" s="3"/>
     </row>
@@ -787,22 +1046,22 @@
       <c r="B152" s="3"/>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B153" s="5"/>
+      <c r="B153" s="3"/>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B154" s="5"/>
+      <c r="B154" s="3"/>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B155" s="5"/>
+      <c r="B155" s="3"/>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B156" s="5"/>
+      <c r="B156" s="3"/>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B157" s="5"/>
+      <c r="B157" s="3"/>
     </row>
     <row r="158" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B158" s="5"/>
+      <c r="B158" s="3"/>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B159" s="3"/>
@@ -3546,113 +3805,86 @@
     <row r="1072" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1072" s="3"/>
     </row>
-    <row r="1073" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1073" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1073" s="3"/>
     </row>
-    <row r="1074" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1074" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1074" s="3"/>
     </row>
-    <row r="1075" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1075" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1075" s="3"/>
     </row>
-    <row r="1076" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1076" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1076" s="3"/>
     </row>
-    <row r="1077" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1077" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1077" s="3"/>
     </row>
-    <row r="1078" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1078" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1078" s="3"/>
     </row>
-    <row r="1079" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1079" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1079" s="3"/>
     </row>
-    <row r="1080" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1080" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1080" s="3"/>
     </row>
-    <row r="1081" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1081" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1081" s="3"/>
     </row>
-    <row r="1082" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1082" s="3"/>
-    </row>
-    <row r="1083" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1083" s="3"/>
-    </row>
-    <row r="1084" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1084" s="3"/>
-    </row>
-    <row r="1085" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1085" s="3"/>
-    </row>
-    <row r="1086" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1086" s="3"/>
-    </row>
-    <row r="1087" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1087" s="3"/>
-    </row>
-    <row r="1088" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1088" s="3"/>
-    </row>
-    <row r="1089" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1089" s="3"/>
-    </row>
-    <row r="1090" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1090" s="3"/>
-    </row>
-    <row r="1091" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1091" s="3"/>
-    </row>
-    <row r="1092" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1092" s="3"/>
-    </row>
-    <row r="1093" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1093" s="3"/>
-    </row>
-    <row r="1094" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1094" s="3"/>
-    </row>
-    <row r="1095" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1095" s="3"/>
-    </row>
-    <row r="1096" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1096" s="3"/>
-    </row>
-    <row r="1097" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1097" s="3"/>
-    </row>
-    <row r="1098" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1098" s="3"/>
-    </row>
-    <row r="1099" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1099" s="3"/>
-    </row>
-    <row r="1100" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1100" s="3"/>
-    </row>
-    <row r="1101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1101" s="3"/>
-    </row>
-    <row r="1102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1102" s="3"/>
-    </row>
-    <row r="1103" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1103" s="3"/>
-    </row>
-    <row r="1104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1104" s="3"/>
-    </row>
-    <row r="1105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1105" s="3"/>
-    </row>
-    <row r="1106" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1106" s="3"/>
-    </row>
-    <row r="1107" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1107" s="3"/>
-    </row>
-    <row r="1108" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1108" s="3"/>
+    <row r="1082" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1082" s="6"/>
+    </row>
+    <row r="1083" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1083" s="6"/>
+    </row>
+    <row r="1084" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1084" s="6"/>
+    </row>
+    <row r="1085" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1085" s="6"/>
+    </row>
+    <row r="1086" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1086" s="6"/>
+    </row>
+    <row r="1087" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1087" s="6"/>
+    </row>
+    <row r="1088" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1088" s="6"/>
+    </row>
+    <row r="1089" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1089" s="6"/>
+    </row>
+    <row r="1090" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1090" s="6"/>
+    </row>
+    <row r="1091" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1091" s="6"/>
+    </row>
+    <row r="1092" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1092" s="6"/>
+    </row>
+    <row r="1093" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1093" s="6"/>
+    </row>
+    <row r="1094" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1094" s="6"/>
+    </row>
+    <row r="1095" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1095" s="6"/>
+    </row>
+    <row r="1098" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1098" s="4"/>
+    </row>
+    <row r="1102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1102" s="4"/>
+    </row>
+    <row r="1103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1103" s="4"/>
+    </row>
+    <row r="1104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1104" s="4"/>
     </row>
     <row r="1109" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1109" s="3"/>
@@ -3690,73 +3922,100 @@
     <row r="1120" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1120" s="3"/>
     </row>
-    <row r="1121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1121" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1121" s="3"/>
     </row>
-    <row r="1122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1122" s="6"/>
-    </row>
-    <row r="1123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1123" s="6"/>
-    </row>
-    <row r="1124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1124" s="6"/>
-    </row>
-    <row r="1125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1125" s="6"/>
-    </row>
-    <row r="1126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1126" s="6"/>
-    </row>
-    <row r="1127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1127" s="6"/>
-    </row>
-    <row r="1128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1128" s="6"/>
-    </row>
-    <row r="1129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1129" s="6"/>
-    </row>
-    <row r="1130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1130" s="6"/>
-    </row>
-    <row r="1131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1131" s="6"/>
-    </row>
-    <row r="1132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1132" s="6"/>
-    </row>
-    <row r="1133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1133" s="6"/>
-    </row>
-    <row r="1134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1134" s="6"/>
-    </row>
-    <row r="1135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1135" s="6"/>
-    </row>
-    <row r="1138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B1138" s="4"/>
-    </row>
-    <row r="1142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1142" s="4"/>
-    </row>
-    <row r="1143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1143" s="4"/>
-    </row>
-    <row r="1144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1144" s="4"/>
-    </row>
-    <row r="1149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1122" s="3"/>
+    </row>
+    <row r="1123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1123" s="3"/>
+    </row>
+    <row r="1124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1124" s="3"/>
+    </row>
+    <row r="1125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1125" s="3"/>
+    </row>
+    <row r="1126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1126" s="5"/>
+    </row>
+    <row r="1127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1127" s="5"/>
+    </row>
+    <row r="1128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1128" s="5"/>
+    </row>
+    <row r="1129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1129" s="3"/>
+    </row>
+    <row r="1130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1130" s="3"/>
+    </row>
+    <row r="1131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1131" s="3"/>
+    </row>
+    <row r="1132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1132" s="3"/>
+    </row>
+    <row r="1133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1133" s="3"/>
+    </row>
+    <row r="1134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1134" s="3"/>
+    </row>
+    <row r="1135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1135" s="3"/>
+    </row>
+    <row r="1136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1136" s="3"/>
+    </row>
+    <row r="1137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1137" s="3"/>
+    </row>
+    <row r="1138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1138" s="3"/>
+    </row>
+    <row r="1139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1139" s="3"/>
+    </row>
+    <row r="1140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1140" s="3"/>
+    </row>
+    <row r="1141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1141" s="3"/>
+    </row>
+    <row r="1142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1142" s="3"/>
+    </row>
+    <row r="1143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1143" s="3"/>
+    </row>
+    <row r="1144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1144" s="3"/>
+    </row>
+    <row r="1145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1145" s="3"/>
+    </row>
+    <row r="1146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1146" s="3"/>
+    </row>
+    <row r="1147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1147" s="3"/>
+    </row>
+    <row r="1148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1148" s="3"/>
+    </row>
+    <row r="1149" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1149" s="3"/>
     </row>
-    <row r="1150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1150" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1150" s="3"/>
     </row>
-    <row r="1151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1151" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1151" s="3"/>
     </row>
-    <row r="1152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1152" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1152" s="3"/>
     </row>
     <row r="1153" spans="2:2" x14ac:dyDescent="0.2">
@@ -3799,13 +4058,13 @@
       <c r="B1165" s="3"/>
     </row>
     <row r="1166" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1166" s="5"/>
+      <c r="B1166" s="3"/>
     </row>
     <row r="1167" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1167" s="5"/>
+      <c r="B1167" s="3"/>
     </row>
     <row r="1168" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1168" s="5"/>
+      <c r="B1168" s="3"/>
     </row>
     <row r="1169" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1169" s="3"/>
@@ -4557,150 +4816,30 @@
     <row r="1418" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1418" s="3"/>
     </row>
-    <row r="1419" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1419" s="3"/>
-    </row>
-    <row r="1420" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1420" s="3"/>
-    </row>
-    <row r="1421" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1421" s="3"/>
-    </row>
-    <row r="1422" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1422" s="3"/>
-    </row>
-    <row r="1423" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1423" s="3"/>
-    </row>
-    <row r="1424" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1424" s="3"/>
-    </row>
-    <row r="1425" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1425" s="3"/>
-    </row>
-    <row r="1426" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1426" s="3"/>
-    </row>
-    <row r="1427" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1427" s="3"/>
-    </row>
-    <row r="1428" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1428" s="3"/>
-    </row>
-    <row r="1429" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1429" s="3"/>
-    </row>
-    <row r="1430" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1430" s="3"/>
-    </row>
-    <row r="1431" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1431" s="3"/>
-    </row>
-    <row r="1432" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1432" s="3"/>
-    </row>
-    <row r="1433" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1433" s="3"/>
-    </row>
-    <row r="1434" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1434" s="3"/>
-    </row>
-    <row r="1435" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1435" s="3"/>
-    </row>
-    <row r="1436" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1436" s="3"/>
-    </row>
-    <row r="1437" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1437" s="3"/>
-    </row>
-    <row r="1438" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1438" s="3"/>
-    </row>
-    <row r="1439" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1439" s="3"/>
-    </row>
-    <row r="1440" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1440" s="3"/>
-    </row>
-    <row r="1441" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1441" s="3"/>
-    </row>
-    <row r="1442" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1442" s="3"/>
-    </row>
-    <row r="1443" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1443" s="3"/>
-    </row>
-    <row r="1444" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1444" s="3"/>
-    </row>
-    <row r="1445" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1445" s="3"/>
-    </row>
-    <row r="1446" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1446" s="3"/>
-    </row>
-    <row r="1447" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1447" s="3"/>
-    </row>
-    <row r="1448" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1448" s="3"/>
-    </row>
-    <row r="1449" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1449" s="3"/>
-    </row>
-    <row r="1450" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1450" s="3"/>
-    </row>
-    <row r="1451" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1451" s="3"/>
-    </row>
-    <row r="1452" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1452" s="3"/>
-    </row>
-    <row r="1453" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1453" s="3"/>
-    </row>
-    <row r="1454" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1454" s="3"/>
-    </row>
-    <row r="1455" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1455" s="3"/>
-    </row>
-    <row r="1456" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1456" s="3"/>
-    </row>
-    <row r="1457" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1457" s="3"/>
-    </row>
-    <row r="1458" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1458" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A159:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+  <conditionalFormatting sqref="A49:A107">
+    <cfRule type="duplicateValues" dxfId="7" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A33:A147">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  <conditionalFormatting sqref="A108:A118">
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A148:A158">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  <conditionalFormatting sqref="A119:A205">
+    <cfRule type="duplicateValues" dxfId="5" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A159:A245">
-    <cfRule type="duplicateValues" dxfId="5" priority="22"/>
+  <conditionalFormatting sqref="A119:A1048576 A1">
+    <cfRule type="duplicateValues" dxfId="4" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A246:A1121">
-    <cfRule type="duplicateValues" dxfId="4" priority="21"/>
+  <conditionalFormatting sqref="A206:A1081">
+    <cfRule type="duplicateValues" dxfId="3" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1122:A1290">
-    <cfRule type="duplicateValues" dxfId="3" priority="20"/>
+  <conditionalFormatting sqref="A1082:A1250">
+    <cfRule type="duplicateValues" dxfId="2" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1291:A1458">
-    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
+  <conditionalFormatting sqref="A1251:A1418">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A32">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A2:A48">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDED9EB8-59EC-428C-8551-005B0C78A379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535A0A2C-A92B-4E30-AFB5-3D94F2227FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -88,7 +85,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,12 +102,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -155,12 +146,11 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -185,6 +175,11 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -528,63 +523,63 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>604068381</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+        <v>814491688</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
-        <v>798534008</v>
+      <c r="A3">
+        <v>697474165</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
-        <v>798533992</v>
+      <c r="A4">
+        <v>599905472</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
-        <v>798533984</v>
+      <c r="A5">
+        <v>763373879</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>798504001</v>
+        <v>758194736</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>798203836</v>
+        <v>814049916</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>793509963</v>
+        <v>812587313</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>808019586</v>
+        <v>812335168</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>3</v>
@@ -592,15 +587,15 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>680116641</v>
+        <v>811069784</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>745159925</v>
+        <v>797805631</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
@@ -608,191 +603,191 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>728349667</v>
+        <v>737346613</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>727195152</v>
+        <v>600280188</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>724049105</v>
+        <v>664724816</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>707531533</v>
+        <v>651547485</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>702783154</v>
+        <v>651413266</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>672864463</v>
+        <v>644978896</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>671257834</v>
+        <v>612274765</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>652845037</v>
+        <v>821244500</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>653050082</v>
+        <v>799066927</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>631890823</v>
+        <v>801053657</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>629690706</v>
+        <v>801052907</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>612368179</v>
+        <v>799933878</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>650269933</v>
+        <v>799413970</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>808019412</v>
+        <v>784602470</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>810178883</v>
+        <v>784143574</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>787150014</v>
+        <v>768449500</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>696563695</v>
+        <v>590199265</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>820703175</v>
+        <v>176762486</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>789375130</v>
+        <v>174520399</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>788966046</v>
+        <v>170994085</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>763951088</v>
+        <v>816888956</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>795440886</v>
+        <v>815524032</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>820863268</v>
+        <v>812913097</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>784673331</v>
+        <v>814998427</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>2</v>
@@ -800,7 +795,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>726339207</v>
+        <v>811611932</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>2</v>
@@ -808,523 +803,1308 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>798394213</v>
+        <v>802565634</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B38" s="3"/>
+      <c r="A38">
+        <v>801356902</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B39" s="3"/>
+      <c r="A39">
+        <v>750254017</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B40" s="3"/>
+      <c r="A40">
+        <v>763843707</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B41" s="3"/>
+      <c r="A41">
+        <v>764661595</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B42" s="3"/>
+      <c r="A42">
+        <v>764423939</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B43" s="3"/>
+      <c r="A43">
+        <v>749451336</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B44" s="3"/>
+      <c r="A44">
+        <v>749347393</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B45" s="3"/>
+      <c r="A45">
+        <v>742734852</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B46" s="3"/>
+      <c r="A46">
+        <v>735976429</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B47" s="3"/>
+      <c r="A47">
+        <v>734893237</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B48" s="3"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="3"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" s="3"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="3"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="3"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="3"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="3"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55" s="3"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B56" s="3"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B57" s="3"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B58" s="3"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B59" s="3"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B60" s="3"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61" s="3"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62" s="3"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63" s="3"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64" s="3"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="3"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B66" s="3"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B67" s="3"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B68" s="3"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B69" s="3"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B70" s="3"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B71" s="3"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B72" s="3"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B73" s="3"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B74" s="3"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75" s="3"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B76" s="3"/>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B77" s="3"/>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B78" s="3"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B79" s="3"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B80" s="3"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81" s="3"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B82" s="3"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" s="3"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B84" s="3"/>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B85" s="3"/>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B86" s="3"/>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B87" s="3"/>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B88" s="3"/>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B89" s="3"/>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B90" s="3"/>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B91" s="3"/>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B92" s="3"/>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B93" s="3"/>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B94" s="3"/>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B95" s="3"/>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B96" s="3"/>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B97" s="3"/>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B98" s="3"/>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B99" s="3"/>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B100" s="3"/>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B101" s="3"/>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B102" s="3"/>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B103" s="3"/>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B104" s="3"/>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B105" s="3"/>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B106" s="3"/>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B107" s="3"/>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B108" s="3"/>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B109" s="3"/>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B110" s="3"/>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B111" s="3"/>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B112" s="3"/>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B113" s="3"/>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B114" s="3"/>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B115" s="3"/>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B116" s="3"/>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B117" s="3"/>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B118" s="3"/>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B119" s="3"/>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B120" s="3"/>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B121" s="3"/>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B122" s="3"/>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B123" s="3"/>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B124" s="3"/>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B125" s="3"/>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B126" s="3"/>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B127" s="3"/>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B128" s="3"/>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B129" s="3"/>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B130" s="3"/>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B131" s="3"/>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B132" s="3"/>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B133" s="3"/>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B134" s="3"/>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B135" s="3"/>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B136" s="3"/>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B137" s="3"/>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B138" s="3"/>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B139" s="3"/>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B140" s="3"/>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B141" s="3"/>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B142" s="3"/>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B143" s="3"/>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B144" s="3"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B145" s="3"/>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B146" s="3"/>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B147" s="3"/>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B148" s="3"/>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B149" s="3"/>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B150" s="3"/>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B151" s="3"/>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B152" s="3"/>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B153" s="3"/>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B154" s="3"/>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B155" s="3"/>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B156" s="3"/>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B157" s="3"/>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B158" s="3"/>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B159" s="3"/>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B160" s="3"/>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B161" s="3"/>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B162" s="3"/>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B163" s="3"/>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B164" s="3"/>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B165" s="3"/>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B166" s="3"/>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B167" s="3"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B168" s="3"/>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B169" s="3"/>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B170" s="3"/>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B171" s="3"/>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B172" s="3"/>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B173" s="3"/>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B174" s="3"/>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B175" s="3"/>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B176" s="3"/>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B177" s="3"/>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B178" s="3"/>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B179" s="3"/>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B180" s="3"/>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B181" s="3"/>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B182" s="3"/>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B183" s="3"/>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B184" s="3"/>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B185" s="3"/>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B186" s="3"/>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B187" s="3"/>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B188" s="3"/>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B189" s="3"/>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B190" s="3"/>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B191" s="3"/>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B192" s="3"/>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B193" s="3"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B194" s="3"/>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>724758275</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>723488577</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>720343122</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>719383949</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>716619832</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>713037608</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>710947064</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>705584534</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>703615389</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>698410952</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>683416196</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>682535582</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>671841686</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>670972565</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>698283466</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>690808054</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>689411571</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>669972980</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>685040895</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>610498002</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>636837860</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>657116368</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>636700407</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>632296301</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>807815398</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>799268481</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>800905170</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>798898197</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>766892271</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>778054670</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>795511090</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>792332599</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>788524027</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>774820231</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>772766188</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>772646679</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>771481474</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>770017394</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>813278789</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>819558317</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>590301531</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>812342867</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>812648560</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>806530501</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>707872713</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>737474134</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>751997028</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>762831356</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>748390022</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>725402238</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>731611798</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>730252420</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>722559683</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>622409161</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>686316534</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>634916674</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>633927169</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>633733831</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>806430991</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>796859464</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>776548608</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>787200025</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>789183427</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>812075673</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>818721403</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>812879728</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>811188170</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>734540895</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>749946574</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>720511090</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>715172353</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>695459671</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>800587879</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>800286563</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>721016370</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>710985452</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>689775108</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>176818767</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>815017797</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>747531477</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>742400868</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>815051093</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>791206513</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>815445808</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>812072043</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>814374686</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>170947265</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>763319591</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>728480884</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>704607849</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>813122136</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>806410910</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>751233291</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>745533970</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>766353670</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>767366739</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>812814667</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>713192718</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>691621217</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>639917834</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>622364929</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>750753422</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>640502237</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>814838987</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>786580609</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>815483791</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>814228767</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>790694446</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>766993129</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>661333884</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>632488148</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>812684284</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>813936212</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>796062101</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>795900210</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>781834423</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>613772148</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>753271380</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>653545511</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>606903163</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>603000005</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>815477454</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>815536846</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>815502186</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>815157775</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>815155332</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>815093400</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>814269266</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>814677583</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>814945857</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>814665455</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>814636498</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>814399451</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>814505685</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>814241315</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>813667551</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>813619388</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>699408799</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>676400470</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>669691358</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>814224238</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>810122592</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>811965338</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>809583184</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>749050831</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>726467206</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>625827682</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B195" s="3"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B196" s="3"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B197" s="3"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B198" s="3"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B199" s="3"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B200" s="3"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B201" s="3"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B202" s="3"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B203" s="3"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B204" s="3"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B205" s="3"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B206" s="3"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B207" s="3"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B208" s="3"/>
     </row>
     <row r="209" spans="2:2" x14ac:dyDescent="0.2">
@@ -4682,25 +5462,19 @@
       <c r="B1335" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A38:A170">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+  <conditionalFormatting sqref="A195:A998">
+    <cfRule type="duplicateValues" dxfId="4" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A171:A186">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A187:A998">
-    <cfRule type="duplicateValues" dxfId="4" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A187:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
+  <conditionalFormatting sqref="A195:A1048576 A1">
+    <cfRule type="duplicateValues" dxfId="3" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A999:A1167">
-    <cfRule type="duplicateValues" dxfId="2" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1168:A1335">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A37">
+  <conditionalFormatting sqref="A2:A194">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535A0A2C-A92B-4E30-AFB5-3D94F2227FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA7AAB5-E2FD-492C-A58C-62E245A63E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">OCORRENCIA_INTERNA                                     </t>
   </si>
   <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
@@ -150,7 +150,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -175,16 +175,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -523,47 +513,47 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>814491688</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>634057610</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>697474165</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>621016694</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>599905472</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>679895312</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>763373879</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>697097396</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>758194736</v>
+        <v>761137458</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>814049916</v>
+        <v>792967949</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>3</v>
@@ -571,15 +561,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>812587313</v>
+        <v>609980259</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>812335168</v>
+        <v>801827316</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>3</v>
@@ -587,7 +577,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>811069784</v>
+        <v>775888088</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>3</v>
@@ -595,7 +585,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>797805631</v>
+        <v>774646834</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
@@ -603,151 +593,151 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>737346613</v>
+        <v>763302886</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>600280188</v>
+        <v>760199731</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>664724816</v>
+        <v>735443677</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>651547485</v>
+        <v>726982238</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>651413266</v>
+        <v>718171378</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>644978896</v>
+        <v>706596586</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>612274765</v>
+        <v>690127729</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>821244500</v>
+        <v>690040773</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>799066927</v>
+        <v>664433335</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>801053657</v>
+        <v>660426192</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>801052907</v>
+        <v>641929017</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>799933878</v>
+        <v>620585814</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>799413970</v>
+        <v>822720201</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>784602470</v>
+        <v>174187637</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>784143574</v>
+        <v>819374210</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>768449500</v>
+        <v>815895184</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>590199265</v>
+        <v>813845645</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>176762486</v>
+        <v>799884790</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>174520399</v>
+        <v>796932493</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>2</v>
@@ -755,7 +745,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>170994085</v>
+        <v>772265041</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>2</v>
@@ -763,7 +753,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>816888956</v>
+        <v>792290029</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
@@ -771,7 +761,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>815524032</v>
+        <v>787169469</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>2</v>
@@ -779,7 +769,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>812913097</v>
+        <v>785594460</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>2</v>
@@ -787,7 +777,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>814998427</v>
+        <v>775780848</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>2</v>
@@ -795,7 +785,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>811611932</v>
+        <v>780459958</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>2</v>
@@ -803,7 +793,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>802565634</v>
+        <v>693395893</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>2</v>
@@ -811,7 +801,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>801356902</v>
+        <v>720181860</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>2</v>
@@ -819,7 +809,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>750254017</v>
+        <v>762836629</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>2</v>
@@ -827,7 +817,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>763843707</v>
+        <v>771948159</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>2</v>
@@ -835,7 +825,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>764661595</v>
+        <v>770941049</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>2</v>
@@ -843,7 +833,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>764423939</v>
+        <v>750524583</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>2</v>
@@ -851,7 +841,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>749451336</v>
+        <v>749681064</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>2</v>
@@ -859,7 +849,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>749347393</v>
+        <v>749258368</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>2</v>
@@ -867,7 +857,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>742734852</v>
+        <v>748612904</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>2</v>
@@ -875,7 +865,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>735976429</v>
+        <v>747164808</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>2</v>
@@ -883,7 +873,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>734893237</v>
+        <v>747117954</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>2</v>
@@ -891,7 +881,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>724758275</v>
+        <v>728084835</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>2</v>
@@ -899,7 +889,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>723488577</v>
+        <v>727516019</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>2</v>
@@ -907,7 +897,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>720343122</v>
+        <v>723332387</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>2</v>
@@ -915,7 +905,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>719383949</v>
+        <v>727168985</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>2</v>
@@ -923,7 +913,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>716619832</v>
+        <v>727021671</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>2</v>
@@ -931,7 +921,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>713037608</v>
+        <v>706744335</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>2</v>
@@ -939,7 +929,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>710947064</v>
+        <v>704316326</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>2</v>
@@ -947,7 +937,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>705584534</v>
+        <v>687935720</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>2</v>
@@ -955,7 +945,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>703615389</v>
+        <v>682570134</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>2</v>
@@ -963,7 +953,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>698410952</v>
+        <v>678714126</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>2</v>
@@ -971,7 +961,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>683416196</v>
+        <v>674719657</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>2</v>
@@ -979,7 +969,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>682535582</v>
+        <v>674138163</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>2</v>
@@ -987,7 +977,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>671841686</v>
+        <v>622440471</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>2</v>
@@ -995,7 +985,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>670972565</v>
+        <v>660661558</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>2</v>
@@ -1003,7 +993,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>698283466</v>
+        <v>672374174</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>2</v>
@@ -1011,7 +1001,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>690808054</v>
+        <v>670082423</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>2</v>
@@ -1019,167 +1009,167 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>689411571</v>
+        <v>657755298</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>669972980</v>
+        <v>657413146</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>685040895</v>
+        <v>655605164</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>610498002</v>
+        <v>653349104</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>636837860</v>
+        <v>636285417</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>657116368</v>
+        <v>635825767</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>636700407</v>
+        <v>634057628</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>632296301</v>
+        <v>815031418</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>807815398</v>
+        <v>605021975</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>799268481</v>
+        <v>612035984</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>800905170</v>
+        <v>601445558</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>798898197</v>
+        <v>822710244</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>766892271</v>
+        <v>822336644</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>778054670</v>
+        <v>822199067</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>795511090</v>
+        <v>811674641</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>792332599</v>
+        <v>807034917</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>788524027</v>
+        <v>807623248</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>774820231</v>
+        <v>640303099</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>772766188</v>
+        <v>686239546</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>772646679</v>
+        <v>736471982</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>771481474</v>
+        <v>813144007</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>3</v>
@@ -1187,924 +1177,379 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>770017394</v>
+        <v>699945717</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <v>813278789</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B86" s="3"/>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <v>819558317</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B87" s="3"/>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <v>590301531</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B88" s="3"/>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>812342867</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B89" s="3"/>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>812648560</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B90" s="3"/>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>806530501</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B91" s="3"/>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92">
-        <v>707872713</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B92" s="3"/>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93">
-        <v>737474134</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B93" s="3"/>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94">
-        <v>751997028</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B94" s="3"/>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95">
-        <v>762831356</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="B95" s="3"/>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96">
-        <v>748390022</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97">
-        <v>725402238</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98">
-        <v>731611798</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99">
-        <v>730252420</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>722559683</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101">
-        <v>622409161</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102">
-        <v>686316534</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103">
-        <v>634916674</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104">
-        <v>633927169</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105">
-        <v>633733831</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106">
-        <v>806430991</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107">
-        <v>796859464</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108">
-        <v>776548608</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>787200025</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110">
-        <v>789183427</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111">
-        <v>812075673</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112">
-        <v>818721403</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113">
-        <v>812879728</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>811188170</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>734540895</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116">
-        <v>749946574</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117">
-        <v>720511090</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>715172353</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>695459671</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120">
-        <v>800587879</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>800286563</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122">
-        <v>721016370</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123">
-        <v>710985452</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>689775108</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125">
-        <v>176818767</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126">
-        <v>815017797</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127">
-        <v>747531477</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128">
-        <v>742400868</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129">
-        <v>815051093</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>791206513</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>815445808</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132">
-        <v>812072043</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>814374686</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>170947265</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>763319591</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136">
-        <v>728480884</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>704607849</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>813122136</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>806410910</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>751233291</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>745533970</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>766353670</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>767366739</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>812814667</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145">
-        <v>713192718</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>691621217</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>639917834</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>622364929</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>750753422</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>640502237</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>814838987</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>786580609</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>815483791</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154">
-        <v>814228767</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155">
-        <v>790694446</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156">
-        <v>766993129</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157">
-        <v>661333884</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158">
-        <v>632488148</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>812684284</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160">
-        <v>813936212</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161">
-        <v>796062101</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162">
-        <v>795900210</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163">
-        <v>781834423</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164">
-        <v>613772148</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165">
-        <v>753271380</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166">
-        <v>653545511</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167">
-        <v>606903163</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168">
-        <v>603000005</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169">
-        <v>815477454</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A170">
-        <v>815536846</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>815502186</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A172">
-        <v>815157775</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A173">
-        <v>815155332</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A174">
-        <v>815093400</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A175">
-        <v>814269266</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A176">
-        <v>814677583</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A177">
-        <v>814945857</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A178">
-        <v>814665455</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A179">
-        <v>814636498</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180">
-        <v>814399451</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181">
-        <v>814505685</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A182">
-        <v>814241315</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A183">
-        <v>813667551</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A184">
-        <v>813619388</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A185">
-        <v>699408799</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A186">
-        <v>676400470</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A187">
-        <v>669691358</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A188">
-        <v>814224238</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A189">
-        <v>810122592</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A190">
-        <v>811965338</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A191">
-        <v>809583184</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A192">
-        <v>749050831</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A193">
-        <v>726467206</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A194">
-        <v>625827682</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" s="3"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B154" s="3"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B155" s="3"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B156" s="3"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162" s="3"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163" s="3"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164" s="3"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165" s="3"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="3"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B172" s="3"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173" s="3"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B174" s="3"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B175" s="3"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" s="3"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" s="3"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180" s="3"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181" s="3"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B187" s="3"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B188" s="3"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B189" s="3"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190" s="3"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B191" s="3"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B192" s="3"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B193" s="3"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B194" s="3"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B195" s="3"/>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B196" s="3"/>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B197" s="3"/>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B198" s="3"/>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B199" s="3"/>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B200" s="3"/>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B201" s="3"/>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B202" s="3"/>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B203" s="3"/>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B204" s="3"/>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B205" s="3"/>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B206" s="3"/>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B207" s="3"/>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B208" s="3"/>
     </row>
     <row r="209" spans="2:2" x14ac:dyDescent="0.2">
@@ -5462,19 +4907,22 @@
       <c r="B1335" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A86:A194">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A195:A998">
-    <cfRule type="duplicateValues" dxfId="4" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A195:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="3" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A999:A1167">
-    <cfRule type="duplicateValues" dxfId="2" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1168:A1335">
-    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A194">
+  <conditionalFormatting sqref="A2:A85">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318CC2B9-D0E7-46E7-9C80-560B2637CF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CED070-31C9-493F-A0B9-3AF991A8E27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -523,7 +523,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>813833294</v>
+        <v>694861364</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>602970125</v>
+        <v>806568501</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>176724320</v>
+        <v>820598351</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>819243019</v>
+        <v>818071403</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>650759917</v>
+        <v>805462102</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -563,15 +563,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>802573778</v>
+        <v>806806968</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>803952823</v>
+        <v>804218208</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>659395762</v>
+        <v>781610195</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>819416771</v>
+        <v>772955781</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>683321180</v>
+        <v>772955773</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>620917264</v>
+        <v>765379072</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>595753785</v>
+        <v>749804773</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -619,7 +619,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>595328224</v>
+        <v>745103543</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -627,7 +627,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>171049145</v>
+        <v>743889218</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -635,7 +635,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>821449794</v>
+        <v>738891781</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>174636849</v>
+        <v>734454865</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>172062329</v>
+        <v>695334395</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>171078466</v>
+        <v>675341055</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>816256600</v>
+        <v>659584712</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -675,7 +675,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>814875450</v>
+        <v>657229153</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -683,7 +683,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>806777888</v>
+        <v>616759324</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -691,103 +691,103 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>805696451</v>
+        <v>617895770</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>798318444</v>
+        <v>772127050</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>780484444</v>
+        <v>823466846</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>768536199</v>
+        <v>821707407</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>752554752</v>
+        <v>820885022</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>749984807</v>
+        <v>818944799</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>749502203</v>
+        <v>817483732</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>746137615</v>
+        <v>817013844</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>745165302</v>
+        <v>789827445</v>
       </c>
       <c r="B31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>736822952</v>
+        <v>696700925</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>733721272</v>
+        <v>715165241</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>705888307</v>
+        <v>738382989</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>734802410</v>
+        <v>742734118</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>819131586</v>
+        <v>711073423</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>653480172</v>
+        <v>701962734</v>
       </c>
       <c r="B37" t="s">
         <v>2</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>674864909</v>
+        <v>639854698</v>
       </c>
       <c r="B38" t="s">
         <v>2</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>663722498</v>
+        <v>639232556</v>
       </c>
       <c r="B39" t="s">
         <v>2</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>662723133</v>
+        <v>633059666</v>
       </c>
       <c r="B40" t="s">
         <v>2</v>
@@ -835,7 +835,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>175469299</v>
+        <v>616589465</v>
       </c>
       <c r="B41" t="s">
         <v>2</v>
@@ -843,47 +843,47 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>820020331</v>
+        <v>614503880</v>
       </c>
       <c r="B42" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>765762962</v>
+        <v>687482798</v>
       </c>
       <c r="B43" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>806881755</v>
+        <v>753170574</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>810484646</v>
+        <v>714561192</v>
       </c>
       <c r="B45" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>780612481</v>
+        <v>711391304</v>
       </c>
       <c r="B46" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>781652825</v>
+        <v>820206591</v>
       </c>
       <c r="B47" t="s">
         <v>2</v>
@@ -891,7 +891,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>781476290</v>
+        <v>707232231</v>
       </c>
       <c r="B48" t="s">
         <v>2</v>
@@ -899,207 +899,207 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>781273671</v>
+        <v>820273435</v>
       </c>
       <c r="B49" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>776179297</v>
+        <v>820087397</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>743270104</v>
+        <v>820287492</v>
       </c>
       <c r="B51" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>759054269</v>
+        <v>819985429</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>752958003</v>
+        <v>803468341</v>
       </c>
       <c r="B53" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>738016900</v>
+        <v>749716852</v>
       </c>
       <c r="B54" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>713194227</v>
+        <v>745987606</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>824545754</v>
+        <v>736879267</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>823496538</v>
+        <v>730446766</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>715888479</v>
+        <v>712058175</v>
       </c>
       <c r="B58" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>689757932</v>
+        <v>697245284</v>
       </c>
       <c r="B59" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>617955467</v>
+        <v>683542272</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>639839624</v>
+        <v>819592506</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>623092388</v>
+        <v>676030343</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>813653916</v>
+        <v>672137175</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>819380662</v>
+        <v>643987476</v>
       </c>
       <c r="B64" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>779599475</v>
+        <v>809424769</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>780757633</v>
+        <v>808034403</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>774366813</v>
+        <v>807757491</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>805792730</v>
+        <v>798463216</v>
       </c>
       <c r="B68" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>819692363</v>
+        <v>748135369</v>
       </c>
       <c r="B69" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>818778841</v>
+        <v>684884012</v>
       </c>
       <c r="B70" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>820530545</v>
+        <v>733296465</v>
       </c>
       <c r="B71" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>769035688</v>
+        <v>685515987</v>
       </c>
       <c r="B72" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>771465261</v>
+        <v>658424829</v>
       </c>
       <c r="B73" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>774574291</v>
+        <v>667870004</v>
       </c>
       <c r="B74" t="s">
         <v>2</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>814272625</v>
+        <v>680963083</v>
       </c>
       <c r="B75" t="s">
         <v>2</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>176834962</v>
+        <v>663947129</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>747425951</v>
+        <v>663220782</v>
       </c>
       <c r="B77" t="s">
         <v>2</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>716548874</v>
+        <v>642454973</v>
       </c>
       <c r="B78" t="s">
         <v>2</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>638595540</v>
+        <v>820594475</v>
       </c>
       <c r="B79" t="s">
         <v>2</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>799180561</v>
+        <v>828688758</v>
       </c>
       <c r="B80" t="s">
         <v>2</v>
@@ -1155,23 +1155,23 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>704348535</v>
+        <v>828654081</v>
       </c>
       <c r="B81" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>613982630</v>
+        <v>819525605</v>
       </c>
       <c r="B82" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>811421530</v>
+        <v>818510244</v>
       </c>
       <c r="B83" t="s">
         <v>2</v>
@@ -1179,41 +1179,91 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>646388284</v>
+        <v>795059553</v>
       </c>
       <c r="B84" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B85" s="3"/>
+      <c r="A85">
+        <v>774746089</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B86" s="3"/>
+      <c r="A86">
+        <v>756448803</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B87" s="3"/>
+      <c r="A87">
+        <v>759820966</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B88" s="3"/>
+      <c r="A88">
+        <v>738220866</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B89" s="3"/>
+      <c r="A89">
+        <v>665214452</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B90" s="3"/>
+      <c r="A90">
+        <v>665913863</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B91" s="3"/>
+      <c r="A91">
+        <v>665001156</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B92" s="3"/>
+      <c r="A92">
+        <v>805889726</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B93" s="3"/>
+      <c r="A93">
+        <v>816911980</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B94" s="3"/>
+      <c r="A94">
+        <v>813865346</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B95" s="3"/>
@@ -4912,25 +4962,22 @@
       <c r="B1335" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A85">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A86:A194">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  <conditionalFormatting sqref="A95:A194">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A195:A998">
-    <cfRule type="duplicateValues" dxfId="4" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A195:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="3" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A999:A1167">
-    <cfRule type="duplicateValues" dxfId="2" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1168:A1335">
-    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A84">
+  <conditionalFormatting sqref="A2:A94">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BFB795-5C6D-45B1-886F-C19D54F9110B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1C1A8E-47F7-4BE8-8E48-42616301E280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -165,7 +165,7 @@
     <cellStyle name="Porcentagem 2" xfId="3" xr:uid="{1BA5571F-FE15-4D41-ACEC-C62287BE7C02}"/>
     <cellStyle name="Vírgula 2" xfId="2" xr:uid="{B4CF277E-FFD1-45D3-9E71-AECE5C216BCF}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -180,6 +180,11 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -295,18 +300,18 @@
             <c:strRef>
               <c:f>Planilha1!$B$1:$B$93</c:f>
               <c:strCache>
-                <c:ptCount val="69"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>OCORRENCIA_INTERNA                                     </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
@@ -318,94 +323,94 @@
                   <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
                 <c:pt idx="35">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
@@ -420,37 +425,37 @@
                   <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
@@ -471,37 +476,52 @@
                   <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1585,88 +1605,88 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>731186999</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
+      <c r="A2">
+        <v>724072271</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>662325236</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
+      <c r="A3">
+        <v>719277984</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>666053420</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>2</v>
+      <c r="A4">
+        <v>775639713</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>682035559</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5">
+        <v>804756298</v>
+      </c>
+      <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>833235512</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6">
+        <v>779394273</v>
+      </c>
+      <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>746771066</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7">
+        <v>772902759</v>
+      </c>
+      <c r="B7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>733110146</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>2</v>
+      <c r="A8">
+        <v>768351003</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>652100490</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>2</v>
+      <c r="A9">
+        <v>750915591</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>642778173</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>2</v>
+      <c r="A10">
+        <v>750071031</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>840035970</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>4</v>
+      <c r="A11">
+        <v>711740260</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>838993123</v>
+        <v>689057812</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
@@ -1674,7 +1694,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>749186403</v>
+        <v>639109812</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -1682,7 +1702,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>744898069</v>
+        <v>173128459</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -1690,7 +1710,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>765421817</v>
+        <v>174787519</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -1698,7 +1718,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>762852832</v>
+        <v>174787493</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -1706,87 +1726,87 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>694001508</v>
+        <v>850330980</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>689452716</v>
+        <v>841905965</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>685608956</v>
+        <v>832876373</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>656481003</v>
+        <v>820343386</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>647189061</v>
+        <v>812037814</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>645475348</v>
+        <v>811315575</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>644344586</v>
+        <v>745558753</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>177286923</v>
+        <v>803410467</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>829237746</v>
+        <v>797224767</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>799906551</v>
+        <v>797160557</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>800818530</v>
+        <v>768320206</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -1794,7 +1814,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>770351488</v>
+        <v>733815041</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -1802,7 +1822,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>733878320</v>
+        <v>632375899</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -1810,7 +1830,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>754941262</v>
+        <v>718498912</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -1818,7 +1838,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>754243610</v>
+        <v>707908350</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -1826,7 +1846,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>751571690</v>
+        <v>706047762</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
@@ -1834,7 +1854,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>639801814</v>
+        <v>685542270</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -1842,7 +1862,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>685705802</v>
+        <v>680470741</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -1850,31 +1870,31 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>708640655</v>
+        <v>804152753</v>
       </c>
       <c r="B35" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>707360842</v>
+        <v>841320660</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>706887431</v>
+        <v>704751845</v>
       </c>
       <c r="B37" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>687216105</v>
+        <v>803557788</v>
       </c>
       <c r="B38" t="s">
         <v>2</v>
@@ -1882,7 +1902,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>678164066</v>
+        <v>771832916</v>
       </c>
       <c r="B39" t="s">
         <v>2</v>
@@ -1890,7 +1910,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>679370944</v>
+        <v>734912110</v>
       </c>
       <c r="B40" t="s">
         <v>2</v>
@@ -1898,7 +1918,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>678185624</v>
+        <v>760221246</v>
       </c>
       <c r="B41" t="s">
         <v>2</v>
@@ -1906,95 +1926,95 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>653148142</v>
+        <v>754854630</v>
       </c>
       <c r="B42" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>845393473</v>
+        <v>829261076</v>
       </c>
       <c r="B43" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>841911781</v>
+        <v>750401360</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>840508646</v>
+        <v>724244623</v>
       </c>
       <c r="B45" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>839146432</v>
+        <v>721156812</v>
       </c>
       <c r="B46" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>840046746</v>
+        <v>706640350</v>
       </c>
       <c r="B47" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>838830465</v>
+        <v>698054792</v>
       </c>
       <c r="B48" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>829255987</v>
+        <v>680109448</v>
       </c>
       <c r="B49" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>826851523</v>
+        <v>643934635</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>824821817</v>
+        <v>591668375</v>
       </c>
       <c r="B51" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>819242730</v>
+        <v>170526861</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>808418424</v>
+        <v>833035847</v>
       </c>
       <c r="B53" t="s">
         <v>2</v>
@@ -2002,7 +2022,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>791603198</v>
+        <v>730993122</v>
       </c>
       <c r="B54" t="s">
         <v>2</v>
@@ -2010,7 +2030,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>777818604</v>
+        <v>808690741</v>
       </c>
       <c r="B55" t="s">
         <v>2</v>
@@ -2018,7 +2038,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>777226089</v>
+        <v>804236762</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
@@ -2026,7 +2046,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>791455391</v>
+        <v>802181879</v>
       </c>
       <c r="B57" t="s">
         <v>2</v>
@@ -2034,7 +2054,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>781321371</v>
+        <v>797300971</v>
       </c>
       <c r="B58" t="s">
         <v>2</v>
@@ -2042,39 +2062,39 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>767334679</v>
+        <v>782758894</v>
       </c>
       <c r="B59" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>765634724</v>
+        <v>781247725</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>756506139</v>
+        <v>780679134</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>662790140</v>
+        <v>763900184</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>688782048</v>
+        <v>758012771</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
@@ -2082,71 +2102,91 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>827828397</v>
+        <v>842859716</v>
       </c>
       <c r="B64" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>842145264</v>
+        <v>828470611</v>
       </c>
       <c r="B65" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>724590207</v>
+        <v>690039791</v>
       </c>
       <c r="B66" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>749590919</v>
+        <v>713100729</v>
       </c>
       <c r="B67" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>805863937</v>
+        <v>829383300</v>
       </c>
       <c r="B68" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>775612918</v>
+        <v>842535233</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
+      <c r="A70">
+        <v>837977143</v>
+      </c>
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
+      <c r="A71">
+        <v>841224946</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
+      <c r="A72">
+        <v>755935743</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
+      <c r="A73">
+        <v>754321804</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
+      <c r="A74">
+        <v>686552492</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
@@ -2552,25 +2592,25 @@
       <c r="B1314" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A70:A84">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+  <conditionalFormatting sqref="A75:A84">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85:A87">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A89:A173">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A174:A371">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1202:A1314">
-    <cfRule type="duplicateValues" dxfId="2" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1202:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A69">
+  <conditionalFormatting sqref="A2:A74">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Descarte.xlsx
+++ b/Treinamento/Planilha Robô Descarte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29016"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{C9460C66-2119-4115-ADBD-AA056ADB35B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B33BBA07-32D0-42CE-A257-AC30C1F1BEB7}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{C9460C66-2119-4115-ADBD-AA056ADB35B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CE436DE-6069-4EF3-A3E4-EB4D40400028}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
 </sst>
 </file>
@@ -284,7 +287,7 @@
             <c:strRef>
               <c:f>Planilha1!$B$1:$B$93</c:f>
               <c:strCache>
-                <c:ptCount val="49"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>OCORRENCIA_INTERNA                                     </c:v>
                 </c:pt>
@@ -295,142 +298,169 @@
                   <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1515,7 +1545,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>762997850</v>
+        <v>724383199</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1523,7 +1553,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>858242963</v>
+        <v>702762570</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -1531,15 +1561,15 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>648371759</v>
+        <v>770949703</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>820571804</v>
+        <v>767220803</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -1547,7 +1577,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>812516049</v>
+        <v>766588960</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -1555,279 +1585,279 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>801857461</v>
+        <v>762291825</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>647180516</v>
+        <v>745906283</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>861485005</v>
+        <v>840055507</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>860782774</v>
+        <v>855532564</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>856139385</v>
+        <v>858335734</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>688797673</v>
+        <v>861511818</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>686740725</v>
+        <v>639125651</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>674040039</v>
+        <v>680116112</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>672661901</v>
+        <v>693028619</v>
       </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>657924753</v>
+        <v>692387412</v>
       </c>
       <c r="B16" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>642340552</v>
+        <v>664782533</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>171357738</v>
+        <v>663636748</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>864959204</v>
+        <v>653255442</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>864469030</v>
+        <v>651227302</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>864439546</v>
+        <v>611863634</v>
       </c>
       <c r="B21" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>598817140</v>
+        <v>864379288</v>
       </c>
       <c r="B22" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>171541745</v>
+        <v>864747831</v>
       </c>
       <c r="B23" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>774756856</v>
+        <v>864736644</v>
       </c>
       <c r="B24" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>778255954</v>
+        <v>863575944</v>
       </c>
       <c r="B25" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>778255236</v>
+        <v>863273136</v>
       </c>
       <c r="B26" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>752206452</v>
+        <v>863066365</v>
       </c>
       <c r="B27" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>751969415</v>
+        <v>862323445</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>741710168</v>
+        <v>862251406</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>740050418</v>
+        <v>852624653</v>
       </c>
       <c r="B30" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>724383207</v>
+        <v>840000610</v>
       </c>
       <c r="B31" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>696923196</v>
+        <v>835682869</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>736879077</v>
+        <v>834525143</v>
       </c>
       <c r="B33" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>736541420</v>
+        <v>812042459</v>
       </c>
       <c r="B34" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>733507820</v>
+        <v>819190764</v>
       </c>
       <c r="B35" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>731832311</v>
+        <v>817801164</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>853085284</v>
+        <v>814793877</v>
       </c>
       <c r="B37" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>842951182</v>
+        <v>810256887</v>
       </c>
       <c r="B38" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>842715389</v>
+        <v>797760281</v>
       </c>
       <c r="B39" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>826663142</v>
+        <v>792073300</v>
       </c>
       <c r="B40" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>828958680</v>
+        <v>790951283</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
@@ -1835,94 +1865,139 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>701374732</v>
+        <v>806406777</v>
       </c>
       <c r="B42" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>725254522</v>
+        <v>789900705</v>
       </c>
       <c r="B43" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>717178291</v>
+        <v>747484081</v>
       </c>
       <c r="B44" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>700675394</v>
+        <v>758769206</v>
       </c>
       <c r="B45" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>777785282</v>
+        <v>770813255</v>
       </c>
       <c r="B46" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>771488743</v>
+        <v>840269777</v>
       </c>
       <c r="B47" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>771427378</v>
+        <v>856811835</v>
       </c>
       <c r="B48" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>746385958</v>
+        <v>662304611</v>
       </c>
       <c r="B49" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="B50" s="4"/>
+      <c r="A50">
+        <v>665266643</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="B51" s="4"/>
+      <c r="A51">
+        <v>681845941</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="B52" s="4"/>
+      <c r="A52">
+        <v>855045047</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="B53" s="4"/>
+      <c r="A53">
+        <v>818334926</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="B54" s="4"/>
+      <c r="A54">
+        <v>833479086</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="B55" s="4"/>
+      <c r="A55">
+        <v>838421471</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="B56" s="4"/>
+      <c r="A56">
+        <v>831119254</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="B57" s="4"/>
+      <c r="A57">
+        <v>825741105</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="B58" s="4"/>
+      <c r="A58">
+        <v>844670012</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="1:2">
       <c r="B59" s="4"/>
@@ -2676,18 +2751,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A248:A371">
-    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1202:A1314">
-    <cfRule type="duplicateValues" dxfId="3" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1202:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="2" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A50:A247">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A59:A247">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A49">
+  <conditionalFormatting sqref="A2:A58">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
